--- a/data/sports/mlb/flat.xlsx
+++ b/data/sports/mlb/flat.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ53" headerRowCount="1">
-  <autoFilter ref="A1:DQ53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ57" headerRowCount="1">
+  <autoFilter ref="A1:DQ57"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$53)</f>
+        <f>COUNTA('Picks'!$A$2:$A$57)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$53,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$57,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$57,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"win")+COUNTIFS('Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$53,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$57,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$57,"&gt;0",'Picks'!$V$2:$V$57,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$57,"&gt;0",'Picks'!$V$2:$V$57,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")/(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$57,"&gt;0",'Picks'!$V$2:$V$57,"win")/(COUNTIFS('Picks'!$BX$2:$BX$57,"&gt;0",'Picks'!$V$2:$V$57,"win")+COUNTIFS('Picks'!$BX$2:$BX$57,"&gt;0",'Picks'!$V$2:$V$57,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$53)/SUM('Picks'!$BX$2:$BX$53),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$57)/SUM('Picks'!$BX$2:$BX$57),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$53)</f>
+        <f>SUM('Picks'!$BY$2:$BY$57)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$53,"&lt;&gt;",'Picks'!$AB$2:$AB$53),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$57,"&lt;&gt;",'Picks'!$AB$2:$AB$57),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$57,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$57,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$53,'Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$57,'Picks'!$AM$2:$AM$57,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A14,'Picks'!$U$2:$U$57,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A14,'Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A14,'Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$57,'Picks'!$H$2:$H$57,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$57,'Picks'!$H$2:$H$57,$A14,'Picks'!$U$2:$U$57,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A15,'Picks'!$U$2:$U$57,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A15,'Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A15,'Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$57,'Picks'!$H$2:$H$57,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$57,'Picks'!$H$2:$H$57,$A15,'Picks'!$U$2:$U$57,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A16,'Picks'!$U$2:$U$57,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A16,'Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$57,$A16,'Picks'!$U$2:$U$57,"settled",'Picks'!$V$2:$V$57,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$57,'Picks'!$H$2:$H$57,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$57,'Picks'!$H$2:$H$57,$A16,'Picks'!$U$2:$U$57,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ53"/>
+  <dimension ref="A1:DQ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21267,6 +21267,1454 @@
       <c r="DP53" s="24" t="n"/>
       <c r="DQ53" s="24" t="n"/>
     </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>a44524dfbbab41b3</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:50:02.772612Z</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T20:00:00-0400</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>401908032</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M54" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.50234</v>
+      </c>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n">
+        <v>-0.117432</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="n"/>
+      <c r="W54" s="26" t="n"/>
+      <c r="X54" s="26" t="n"/>
+      <c r="Y54" s="25" t="n"/>
+      <c r="Z54" s="26" t="n"/>
+      <c r="AA54" s="28" t="n"/>
+      <c r="AB54" s="28" t="n"/>
+      <c r="AC54" s="30" t="n"/>
+      <c r="AD54" s="24" t="n"/>
+      <c r="AE54" s="31" t="inlineStr">
+        <is>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6200 (aec-mlb-mil-lad-2026-10-14); model edge vs ask -0.1177.</t>
+        </is>
+      </c>
+      <c r="AF54" s="31" t="inlineStr">
+        <is>
+          <t>Learned model; shadow-qualified via operator override.</t>
+        </is>
+      </c>
+      <c r="AG54" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH54" s="24" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="n"/>
+      <c r="AK54" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL54" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM54" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN54" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO54" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_BELOW_LEARNED_CONFIDENCE</t>
+        </is>
+      </c>
+      <c r="AP54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AQ54" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AR54" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AS54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AT54" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AU54" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AV54" s="24" t="n"/>
+      <c r="AW54" s="24" t="n"/>
+      <c r="AX54" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY54" s="24" t="n"/>
+      <c r="AZ54" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA54" s="24" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="BB54" s="24" t="inlineStr">
+        <is>
+          <t>learned_lr</t>
+        </is>
+      </c>
+      <c r="BC54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="BD54" s="24" t="inlineStr">
+        <is>
+          <t>3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8</t>
+        </is>
+      </c>
+      <c r="BE54" s="24" t="inlineStr">
+        <is>
+          <t>73d276b25a216730</t>
+        </is>
+      </c>
+      <c r="BF54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG54" s="24" t="inlineStr">
+        <is>
+          <t>mlb-elo-trend-lr-v8</t>
+        </is>
+      </c>
+      <c r="BH54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:36:44.504334Z</t>
+        </is>
+      </c>
+      <c r="BI54" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ54" s="25" t="n"/>
+      <c r="BK54" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL54" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM54" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN54" s="28" t="n">
+        <v>0.616915</v>
+      </c>
+      <c r="BO54" s="28" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n"/>
+      <c r="BR54" s="28" t="n"/>
+      <c r="BS54" s="28" t="n"/>
+      <c r="BT54" s="28" t="n"/>
+      <c r="BU54" s="25" t="n"/>
+      <c r="BV54" s="29" t="n"/>
+      <c r="BW54" s="24" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
+      <c r="BZ54" s="24" t="n"/>
+      <c r="CA54" s="31" t="n"/>
+      <c r="CB54" s="24" t="n"/>
+      <c r="CC54" s="24" t="inlineStr">
+        <is>
+          <t>0.5032338966</t>
+        </is>
+      </c>
+      <c r="CD54" s="24" t="inlineStr">
+        <is>
+          <t>-0.359572</t>
+        </is>
+      </c>
+      <c r="CE54" s="24" t="inlineStr">
+        <is>
+          <t>1.023</t>
+        </is>
+      </c>
+      <c r="CF54" s="24" t="inlineStr">
+        <is>
+          <t>1.007</t>
+        </is>
+      </c>
+      <c r="CG54" s="24" t="n"/>
+      <c r="CH54" s="24" t="n"/>
+      <c r="CI54" s="24" t="n"/>
+      <c r="CJ54" s="24" t="inlineStr">
+        <is>
+          <t>-0.426595</t>
+        </is>
+      </c>
+      <c r="CK54" s="24" t="n"/>
+      <c r="CL54" s="24" t="inlineStr">
+        <is>
+          <t>-0.210268</t>
+        </is>
+      </c>
+      <c r="CM54" s="24" t="inlineStr">
+        <is>
+          <t>-0.4205</t>
+        </is>
+      </c>
+      <c r="CN54" s="24" t="n"/>
+      <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
+      <c r="CQ54" s="24" t="n"/>
+      <c r="CR54" s="24" t="inlineStr">
+        <is>
+          <t>0.50234</t>
+        </is>
+      </c>
+      <c r="CS54" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT54" s="24" t="n"/>
+      <c r="CU54" s="24" t="n"/>
+      <c r="CV54" s="24" t="n"/>
+      <c r="CW54" s="24" t="n"/>
+      <c r="CX54" s="24" t="n"/>
+      <c r="CY54" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:36:44.504334Z</t>
+        </is>
+      </c>
+      <c r="CZ54" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="DA54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="DB54" s="24" t="inlineStr">
+        <is>
+          <t>decision_time_executable_quote</t>
+        </is>
+      </c>
+      <c r="DC54" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DD54" s="24" t="inlineStr">
+        <is>
+          <t>1fddf5b0fa54c67a6f9ca44ef3359bb6fbb9693c751441a660d3e4e2944a3dbf</t>
+        </is>
+      </c>
+      <c r="DE54" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\data\odds\mlb\2026-10-14\polymarket_snapshots.jsonl</t>
+        </is>
+      </c>
+      <c r="DF54" s="24" t="inlineStr">
+        <is>
+          <t>1fddf5b0fa54c67a6f9ca44ef3359bb6fbb9693c751441a660d3e4e2944a3dbf</t>
+        </is>
+      </c>
+      <c r="DG54" s="24" t="n"/>
+      <c r="DH54" s="24" t="n"/>
+      <c r="DI54" s="24" t="n"/>
+      <c r="DJ54" s="24" t="n"/>
+      <c r="DK54" s="24" t="n"/>
+      <c r="DL54" s="24" t="n"/>
+      <c r="DM54" s="24" t="n"/>
+      <c r="DN54" s="24" t="n"/>
+      <c r="DO54" s="24" t="n"/>
+      <c r="DP54" s="24" t="n"/>
+      <c r="DQ54" s="24" t="inlineStr">
+        <is>
+          <t>{"adjustment": {"applied": false, "method": "identity", "reason": "not_applicable"}, "artifact": {"artifact_hash": "3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8", "market_models": {"moneyline": {"coefficients": [3.0404972651, -0.0248808023, -0.9016764146, -0.2981045997, -0.0190272663, 0.1519919276], "confidence_threshold": 0.61966524, "feature_names": ["elo_probability", "trend_gap", "park_factor", "weather_factor", "starter_era_gap", "bullpen_weakness_gap"], "intercept": -0.2831037846, "positive_class": "home"}}, "method": "logistic_regression", "model_version": "mlb-elo-trend-lr-v8", "qualification": {"brier_score": 0.246354, "called_rate": 0.106398, "calls": 148, "failures": ["validation Brier regressed vs incumbent v7 feature set (0.24702 vs 0.24655) even though locked-holdout metrics clear the bar (0.6081 hit rate, 148 calls) -- disqualified under docs/AGENTS.md's promotion rule (a validation regression is not overridable by a good holdout number, since doing so is exactly 'peeking at holdout'). See qualification.validation_regression_note and training.promotion_rationale for the real numbers and the operator-directed override reasoning."], "framework": "locked_complete_date_60_20_20", "hit_rate": 0.608108, "hits": 90, "locked_holdout": true, "market_type": "moneyline", "meets_primary_holdout_metrics": true, "minimum_calls": 50, "minimum_hit_rate": 0.6, "qualification_eligible": true, "qualified": false, "sample_size": 1391, "training_data_note": "starter_era_gap depends on data/mlb_statsapi/game_snapshots.jsonl, kept current as of this artifact's build by cli.py's daily _capture_mlb_starter_snapshots step (added 2026-08-04, same day as this artifact) -- verify that capture is still running before trusting this feature live.", "units_at_minus_110": 23.818182, "validation_brier_score": 0.24702, "validation_brier_score_vs_incumbent": 0.00047, "validation_regression_note": "Validation Brier is WORSE than v7's incumbent feature set (0.24702 vs v7's 0.24655) while locked-holdout is better (0.24635 vs v7's 0.24763). This is the exact 'peek at holdout' pattern docs/AGENTS.md's promotion rule exists to catch -- promoted anyway by explicit operator directive 2026-08-04, not because it cleared this project's own automatic promotion bar. See training.promotion_rationale."}, "schema_version": "1", "sport": "mlb", "training": {"coefficient_fit": {"end": "2025-07-22", "observations": 3814, "start": "2024-04-06"}, "locked_holdout": {"end": "2026-07-29", "observations": 1391, "start": "2026-04-11"}, "market_inputs_used": false, "promotion_rationale": "Operator-directed promotion, 2026-08-04. Real walk-forward ablation (build_walk_forward_rows + chronological_split, matching v7's own methodology, self-consistency-verified by reproducing v7's exact stored holdout numbers before this comparison) replaced pitcher_era_gap (team-level rolling runs-allowed) with starter_era_gap (real per-starter rolling ERA from mlb_statsapi boxscore history, features/starter_history.py) -- the 'different functional form' docs/MODEL_IMPROVEMENTS.md's 'Rank-1 tested honestly' section flagged as worth trying after the additive form (adding starter_era_gap alongside pitcher_era_gap) showed the same validation/holdout disagreement tested 2026-08-02. Coefficient sign is correct (worse starter ERA -&gt; lower home win probability) in both the additive and replacement forms. Real numbers: locked-holdout hit_rate 0.6081 (148 calls, 90 hits) vs v7's +0.6242-threshold 0.6194. Not a clean automatic pass -- see qualification.validation_regression_note.", "threshold_selection": {"end": "2026-04-10", "observations": 1082, "start": "2025-07-23"}, "threshold_source": "validation cohort; never locked holdout", "walk_forward_features": true}}, "artifact_hash": "3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8", "base_home_probability": 0.5023398740151511, "event_id": "401908032", "event_start_utc": "2026-10-15T00:00:00+00:00", "features": {"bullpen_weakness_gap": -0.210268, "elo_probability": 0.5032338966034758, "park_factor": 1.023, "starter_era_gap": -0.4205, "trend_gap": -0.359572, "weather_factor": 1.007}, "historical_source_observation_times_verified": false, "model_version": "mlb-elo-trend-lr-v8", "observed_at_utc": "2026-10-14T05:50:02.772612+00:00", "schema": "learned-moneyline-replay-v1", "served_home_probability": 0.5023398740151511, "snapshot_hash": "712ab046697ae848ddeed982a7dd1b3fea62e3f96ea1498c3534a5359ec6b5a0"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>2639f8d3ead94bd9</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:03.681835Z</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00Z</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>401908032</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>nrfi</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>yrfi</t>
+        </is>
+      </c>
+      <c r="J55" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M55" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N55" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O55" s="28" t="n">
+        <v>0.4812</v>
+      </c>
+      <c r="P55" s="28" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q55" s="28" t="n">
+        <v>0.020371</v>
+      </c>
+      <c r="R55" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S55" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nrfi-v4</t>
+        </is>
+      </c>
+      <c r="U55" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V55" s="24" t="n"/>
+      <c r="W55" s="26" t="n"/>
+      <c r="X55" s="26" t="n"/>
+      <c r="Y55" s="25" t="n"/>
+      <c r="Z55" s="26" t="n"/>
+      <c r="AA55" s="28" t="n"/>
+      <c r="AB55" s="28" t="n"/>
+      <c r="AC55" s="30" t="n"/>
+      <c r="AD55" s="24" t="n"/>
+      <c r="AE55" s="31" t="inlineStr">
+        <is>
+          <t>MLB 1st Inning YRFI: p=0.481 vs ask 0.460 (astatc-mlb-mil-lad-2026-10-14-yrfi; edge +0.0212) (mlb-nrfi-v4, 4272 training games)</t>
+        </is>
+      </c>
+      <c r="AF55" s="31" t="inlineStr">
+        <is>
+          <t>1st inning variance, leadoff home run risk</t>
+        </is>
+      </c>
+      <c r="AG55" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH55" s="24" t="n"/>
+      <c r="AI55" s="31" t="n"/>
+      <c r="AJ55" s="31" t="n"/>
+      <c r="AK55" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL55" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM55" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN55" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO55" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AQ55" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AR55" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AS55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AT55" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AU55" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AV55" s="24" t="n"/>
+      <c r="AW55" s="24" t="n"/>
+      <c r="AX55" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY55" s="24" t="n"/>
+      <c r="AZ55" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA55" s="24" t="inlineStr">
+        <is>
+          <t>cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff</t>
+        </is>
+      </c>
+      <c r="BB55" s="24" t="inlineStr">
+        <is>
+          <t>half_inning_interaction</t>
+        </is>
+      </c>
+      <c r="BC55" s="24" t="inlineStr">
+        <is>
+          <t>mlb-nrfi-v4</t>
+        </is>
+      </c>
+      <c r="BD55" s="24" t="inlineStr">
+        <is>
+          <t>cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff</t>
+        </is>
+      </c>
+      <c r="BE55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF55" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG55" s="24" t="inlineStr">
+        <is>
+          <t>scalar-artifact-replay-v1</t>
+        </is>
+      </c>
+      <c r="BH55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:36:04.233595Z</t>
+        </is>
+      </c>
+      <c r="BI55" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ55" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK55" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL55" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM55" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN55" s="28" t="n"/>
+      <c r="BO55" s="28" t="n"/>
+      <c r="BP55" s="25" t="n"/>
+      <c r="BQ55" s="27" t="n"/>
+      <c r="BR55" s="28" t="n"/>
+      <c r="BS55" s="28" t="n"/>
+      <c r="BT55" s="28" t="n"/>
+      <c r="BU55" s="25" t="n"/>
+      <c r="BV55" s="29" t="n"/>
+      <c r="BW55" s="24" t="n"/>
+      <c r="BX55" s="30" t="n"/>
+      <c r="BY55" s="27" t="n"/>
+      <c r="BZ55" s="24" t="n"/>
+      <c r="CA55" s="31" t="n"/>
+      <c r="CB55" s="24" t="n"/>
+      <c r="CC55" s="24" t="n"/>
+      <c r="CD55" s="24" t="n"/>
+      <c r="CE55" s="24" t="n"/>
+      <c r="CF55" s="24" t="n"/>
+      <c r="CG55" s="24" t="n"/>
+      <c r="CH55" s="24" t="n"/>
+      <c r="CI55" s="24" t="n"/>
+      <c r="CJ55" s="24" t="n"/>
+      <c r="CK55" s="24" t="n"/>
+      <c r="CL55" s="24" t="n"/>
+      <c r="CM55" s="24" t="n"/>
+      <c r="CN55" s="24" t="n"/>
+      <c r="CO55" s="24" t="n"/>
+      <c r="CP55" s="24" t="n"/>
+      <c r="CQ55" s="24" t="n"/>
+      <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT55" s="24" t="n"/>
+      <c r="CU55" s="24" t="n"/>
+      <c r="CV55" s="24" t="n"/>
+      <c r="CW55" s="24" t="n"/>
+      <c r="CX55" s="24" t="n"/>
+      <c r="CY55" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T04:36:04.233595Z</t>
+        </is>
+      </c>
+      <c r="CZ55" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="DA55" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="DB55" s="24" t="inlineStr">
+        <is>
+          <t>decision_time_executable_quote</t>
+        </is>
+      </c>
+      <c r="DC55" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DD55" s="24" t="inlineStr">
+        <is>
+          <t>617a759a29e9d2ea3d7f9c2c21680515363c9c2a804f3659ea7474b48ecc1ca8</t>
+        </is>
+      </c>
+      <c r="DE55" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\data\odds\mlb\2026-10-14\polymarket_snapshots.jsonl</t>
+        </is>
+      </c>
+      <c r="DF55" s="24" t="inlineStr">
+        <is>
+          <t>617a759a29e9d2ea3d7f9c2c21680515363c9c2a804f3659ea7474b48ecc1ca8</t>
+        </is>
+      </c>
+      <c r="DG55" s="24" t="n"/>
+      <c r="DH55" s="24" t="n"/>
+      <c r="DI55" s="24" t="n"/>
+      <c r="DJ55" s="24" t="n"/>
+      <c r="DK55" s="24" t="n"/>
+      <c r="DL55" s="24" t="n"/>
+      <c r="DM55" s="24" t="n"/>
+      <c r="DN55" s="24" t="n"/>
+      <c r="DO55" s="24" t="n"/>
+      <c r="DP55" s="24" t="n"/>
+      <c r="DQ55" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact": {"C": 1.0, "artifact_hash": "cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff", "coef_away": [-0.15092599233710682, 0.33375332491407694, 0.052641650764709516, 0.012200963333336163, -0.044124086984268916, -0.18338539828154118, -0.011069775160598767, -0.07334888990228486, 0.2843164406703071, -0.016022382971498418, -0.42919391686573305, -0.13322539735898248], "coef_home": [-0.056762054222791236, 0.1634913765713207, -0.12677479939259476, -0.10980892029364075, 0.0675840668410901, -0.2155237746431725, -0.0015823333282579347, -0.0017682883771573481, 0.30292713155931383, -0.26515719099464424, -0.24182390473213353, 0.146893598319729], "feature_names": ["top3_composite", "starter_opp_1st_runs", "starter_fip", "starter_k_pct", "starter_bb_pct", "park_1st_runs", "top3_same_hand_share", "team_1st_scored", "top3_park_interaction", "whiff_power_interaction", "starter_park_interaction", "fip_k_ratio"], "fit_n_games": 4272, "intercept_away": 1.0122829388370416, "intercept_home": 0.8796220049130925, "league": "MLB", "market_type": "nrfi", "method": "half_inning_interaction", "model_version": "mlb-nrfi-v4", "note": "Production-qualified MLB first-inning interaction component model replacing mlb-nrfi-v3.", "positive_class": "nrfi", "qualification": {"binary_accuracy": 0.5485, "calibration_ece": 0.021121, "framework": "half_inning_interaction_holdout", "holdout_brier_score": 0.247866, "holdout_log_loss": 0.688855, "locked_holdout": true, "note": "Two-half-inning decomposed model with non-linear interaction features (park, strikeout-whiff, platoon hand alignment) evaluated on 1,424 locked holdout test games.", "qualified": true, "sample_size": 1424, "status": "qualified"}, "scaler_mean_away": [0.10693852528089877, 0.5160531601123584, 3.887999765917613, 0.22160819288389438, 0.07721193820224699, 1.0095550561797733, 0.5512290262172258, 0.4530846910112346, 0.10797593867883881, 0.0832338340753744, 0.522421086896067, 12.74853166149649], "scaler_mean_home": [0.10687735955056178, 0.4668664091760332, 3.880392556179783, 0.22145009363295864, 0.07637907303370803, 1.0095550561797733, 0.5500498361423202, 0.5488433520599267, 0.10794226697635774, 0.08320755243679794, 0.47126779163623655, 12.714614928114717], "scaler_scale_away": [0.0048171779396999235, 0.12136652246642901, 1.0539601780342398, 0.05165113643883803, 0.02673985154876719, 0.09232773263326173, 0.10967171480498189, 0.0982166066212668, 0.01119895692211545, 0.0065842717464252515, 0.13841807595534883, 5.363640846622892], "scaler_scale_home": [0.0049927679114434974, 0.11700796360197874, 1.0206033876941032, 0.052293646761000234, 0.02791997429590162, 0.09232773263326173, 0.11057352848346676, 0.10479111868852325, 0.011525124767030699, 0.006780208072838942, 0.12566593459901798, 5.16406006135981], "schema_version": "2", "sport": "mlb"}, "artifact_hash": "cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff", "engine_source_sha256": "0d1788de892d97e815079a85f389a8dcfd16276fa807f5d446a8a943717fd8da", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "features": {"away_starter_bb_pct": 0.068, "away_starter_days_rest": 6.0, "away_starter_fip": 4.011, "away_starter_k_pct": 0.2039, "away_starter_opp_1st_runs": 0.3185, "away_starter_starts": 3.2958, "away_team_1st_allowed_away": 0.3905, "away_team_1st_scored_away": 0.4186, "away_top3_composite": 0.10642, "home_starter_bb_pct": 0.1018, "home_starter_days_rest": 6.0, "home_starter_fip": 2.288, "home_starter_k_pct": 0.3219, "home_starter_opp_1st_runs": 0.3549, "home_starter_starts": 3.7136, "home_team_1st_allowed_home": 0.5969, "home_team_1st_scored_home": 0.7213, "home_top3_composite": 0.11451, "park_1st_runs": 1.2151}, "historical_source_observation_times_verified": false, "inference_inputs": {}, "model_version": "mlb-nrfi-v4", "observed_at_utc": "2026-10-14T05:51:03.681835+00:00", "replay_scope": "Exact final classifier/distribution inputs and artifact. Upstream historical feature construction not certified.", "schema": "scalar-artifact-replay-v1", "snapshot_hash": "e58f5355b1efd31ad2cf319a5a51a26cf1b3bd241959f525dbcbac1d16bed90b"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>2dbd181ed5c2485b</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:02.821322Z</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00Z</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>401908032</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J56" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K56" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="M56" s="27" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="N56" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="O56" s="28" t="n">
+        <v>0.597065</v>
+      </c>
+      <c r="P56" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q56" s="28" t="n">
+        <v>0.012003</v>
+      </c>
+      <c r="R56" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="S56" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="U56" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V56" s="24" t="n"/>
+      <c r="W56" s="26" t="n"/>
+      <c r="X56" s="26" t="n"/>
+      <c r="Y56" s="25" t="n"/>
+      <c r="Z56" s="26" t="n"/>
+      <c r="AA56" s="28" t="n"/>
+      <c r="AB56" s="28" t="n"/>
+      <c r="AC56" s="30" t="n"/>
+      <c r="AD56" s="24" t="n"/>
+      <c r="AE56" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Margin: Trend Engine projected 3.71-4.15; raw selected-side p=0.6424, calibrated p=0.5971.</t>
+        </is>
+      </c>
+      <c r="AF56" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG56" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH56" s="24" t="n"/>
+      <c r="AI56" s="31" t="n"/>
+      <c r="AJ56" s="31" t="n"/>
+      <c r="AK56" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL56" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM56" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN56" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO56" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AQ56" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AR56" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AS56" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AT56" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AU56" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AV56" s="24" t="n"/>
+      <c r="AW56" s="24" t="n"/>
+      <c r="AX56" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY56" s="24" t="n"/>
+      <c r="AZ56" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA56" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BB56" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC56" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-margin-v3</t>
+        </is>
+      </c>
+      <c r="BD56" s="24" t="inlineStr">
+        <is>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+        </is>
+      </c>
+      <c r="BE56" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF56" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG56" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:02.821322Z</t>
+        </is>
+      </c>
+      <c r="BI56" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ56" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK56" s="26" t="n">
+        <v>-141</v>
+      </c>
+      <c r="BL56" s="27" t="n">
+        <v>1.70922</v>
+      </c>
+      <c r="BM56" s="28" t="n">
+        <v>0.585062</v>
+      </c>
+      <c r="BN56" s="28" t="n">
+        <v>0.58209</v>
+      </c>
+      <c r="BO56" s="28" t="n"/>
+      <c r="BP56" s="25" t="n"/>
+      <c r="BQ56" s="27" t="n"/>
+      <c r="BR56" s="28" t="n"/>
+      <c r="BS56" s="28" t="n"/>
+      <c r="BT56" s="28" t="n"/>
+      <c r="BU56" s="25" t="n"/>
+      <c r="BV56" s="29" t="n"/>
+      <c r="BW56" s="24" t="n"/>
+      <c r="BX56" s="30" t="n"/>
+      <c r="BY56" s="27" t="n"/>
+      <c r="BZ56" s="24" t="n"/>
+      <c r="CA56" s="31" t="n"/>
+      <c r="CB56" s="24" t="n"/>
+      <c r="CC56" s="24" t="n"/>
+      <c r="CD56" s="24" t="n"/>
+      <c r="CE56" s="24" t="n"/>
+      <c r="CF56" s="24" t="n"/>
+      <c r="CG56" s="24" t="n"/>
+      <c r="CH56" s="24" t="n"/>
+      <c r="CI56" s="24" t="n"/>
+      <c r="CJ56" s="24" t="n"/>
+      <c r="CK56" s="24" t="n"/>
+      <c r="CL56" s="24" t="n"/>
+      <c r="CM56" s="24" t="n"/>
+      <c r="CN56" s="24" t="n"/>
+      <c r="CO56" s="24" t="n"/>
+      <c r="CP56" s="24" t="n"/>
+      <c r="CQ56" s="24" t="n"/>
+      <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT56" s="24" t="inlineStr">
+        <is>
+          <t>a9b23362b31654324ebb68d50a78c7a7cbb34dedfe01df9a0d6220e66c25ca47</t>
+        </is>
+      </c>
+      <c r="CU56" s="24" t="inlineStr">
+        <is>
+          <t>7da9fbc6da4044536749c6fcd9abae7c13da55057708570036207f0597844565</t>
+        </is>
+      </c>
+      <c r="CV56" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\model.yaml</t>
+        </is>
+      </c>
+      <c r="CW56" s="24" t="inlineStr">
+        <is>
+          <t>1ac81f4be213944a7cce95cbe9a52520e640a9cc5ea1424409aeda60b059f716</t>
+        </is>
+      </c>
+      <c r="CX56" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\models\measured-edge-margin-v3.json</t>
+        </is>
+      </c>
+      <c r="CY56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:02.821322Z</t>
+        </is>
+      </c>
+      <c r="CZ56" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="DA56" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="DB56" s="24" t="inlineStr">
+        <is>
+          <t>decision_time_executable_quote</t>
+        </is>
+      </c>
+      <c r="DC56" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DD56" s="24" t="inlineStr">
+        <is>
+          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
+        </is>
+      </c>
+      <c r="DE56" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\data\market_odds_snapshots.jsonl</t>
+        </is>
+      </c>
+      <c r="DF56" s="24" t="inlineStr">
+        <is>
+          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
+        </is>
+      </c>
+      <c r="DG56" s="24" t="inlineStr">
+        <is>
+          <t>live_forecast</t>
+        </is>
+      </c>
+      <c r="DH56" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DI56" s="24" t="inlineStr">
+        <is>
+          <t>0.597065</t>
+        </is>
+      </c>
+      <c r="DJ56" s="24" t="inlineStr">
+        <is>
+          <t>0.5850622406639003</t>
+        </is>
+      </c>
+      <c r="DK56" s="24" t="inlineStr">
+        <is>
+          <t>0.597065</t>
+        </is>
+      </c>
+      <c r="DL56" s="24" t="n"/>
+      <c r="DM56" s="24" t="n"/>
+      <c r="DN56" s="24" t="n"/>
+      <c r="DO56" s="24" t="n"/>
+      <c r="DP56" s="24" t="n"/>
+      <c r="DQ56" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact": {"artifact_hash": "dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c", "base_score_model_version": "mlb-analyst-poisson-trend-v0.3", "calibration_method": "flat_probability_shrinkage_toward_half", "calibration_note": "Rebuilt against mlb-analyst-poisson-trend-v0.3's refit elasticities (scripts/mlb_elasticity_refit.py) and fresh game data (scripts/mlb_measured_edge_calibrate.py). Primary fit (this artifact's top-level scale/offset) is OLS of the rebuilt formula's raw simulated cover probability against real game outcomes over 290 games from data/historical/mlb_market_lines_reconstructed.jsonl -- ESPN's own postgame pickcenter reconstruction, hard-labeled timestamp_valid=False by ingest.py::reconstruct_mlb_markets; diagnostic only, NOT real historical Polymarket lines (correcting v1's calibration_note, which mischaracterized this same data source). Correlation with real outcomes: 0.208. Flat -110 diagnostic: {'picks': 285, 'hit_rate': 0.6, 'units': 41.45}. Real-market (genuine captured Polymarket BBO) corroboration: 65 games, scale=0.7458, offset=0.1271, correlation=0.2197, flat -110: {'picks': 63, 'hit_rate': 0.6349, 'units': 13.36}.", "calibration_version": "measured-edge-margin-v3", "calibration_windows": {"diagnostic": {"correlation": 0.208, "flat_110_diagnostic": {"hit_rate": 0.6, "picks": 285, "units": 41.45}, "games": 290, "offset": 0.1593, "scale": 0.6814}, "real_market": {"correlation": 0.2197, "flat_110_diagnostic": {"hit_rate": 0.6349, "picks": 63, "units": 13.36}, "games": 65, "offset": 0.1271, "scale": 0.7458}}, "model_name": "Measured Edge Margin", "model_version": "measured-edge-margin-v3", "offset": 0.1593, "scale": 0.6814, "trained_on_games": 290}, "artifact_hash": "dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c", "away_spread_line": 1.5, "code_sha256": "58bccd1bb97abfc14ea818deb7642e49ab5cbaa6126f4e3d79f33944ad129267", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "features": {"away_bullpen_status": "available", "away_bullpen_weakness": 0.754003, "away_form": {"losses": 1, "runs_allowed": [2, 3, 4, 1, 1, 4], "runs_scored": [3, 4, 3, 3, 2, 7], "status": "available", "wins": 5}, "away_starter": {"last_five_batters_faced": 103, "last_five_earned_runs": 4, "last_five_innings": 26.666666666666668, "last_five_strikeouts": 24, "last_five_walks": 9, "name": "Robert Gasser", "player_id": "4918251", "season_batters_faced": 480, "season_earned_runs": 48, "season_innings": 113.33333333333333, "season_strikeouts": 106, "season_walks": 36, "starts_before_game": 22, "status": "available", "throwing_hand": "Left", "xfip": null, "xfip_status": "unavailable_from_source"}, "away_team": "Milwaukee Brewers", "decision_timestamp_utc": "2026-10-14T22:00:00Z", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "feature_snapshot_hash": "06de8ae80fc43255f9854b4a269c27e6d8d74fe3dfe9e0571a3b9e29b200f020", "home_bullpen_status": "available", "home_bullpen_weakness": 0.543735, "home_form": {"losses": 3, "runs_allowed": [3, 3, 1, 1, 2, 7], "runs_scored": [5, 2, 3, 4, 1, 4], "status": "available", "wins": 3}, "home_starter": {"last_five_batters_faced": 83, "last_five_earned_runs": 3, "last_five_innings": 20.333333333333332, "last_five_strikeouts": 24, "last_five_walks": 9, "name": "Blake Snell", "player_id": "33748", "season_batters_faced": 192, "season_earned_runs": 10, "season_innings": 46.333333333333336, "season_strikeouts": 60, "season_walks": 21, "starts_before_game": 10, "status": "available", "throwing_hand": "Left", "xfip": null, "xfip_status": "unavailable_from_source"}, "home_team": "Los Angeles Dodgers", "lineup_status": "unavailable_from_source", "market_snapshot_hash": "41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0", "park_factor": 1.023, "park_factor_status": "available", "source_snapshot_ids": ["426e4caf3db52fcf13cc3d6110c0c8dfebb17f6e012c71d62e9c5f829d28d875", "5bee6548d750c58ecc0b04fb053bc490a4ba53b6b358c42f57ee6e304a879559", "efcd7d616be57175fbdd44471560ac1ae76d24b89f6a254360415994460b696e", "f1a7e31918b14d7624dbfd79cab472bc83bcbc72378dbf3017f6cb119f29cb6e", "cd3f9d3d1878bc5d0763fa220c7d747cc9c72ac8692a20d370c4a8aaa613db7b"], "starter_confirmed": false, "starter_status": "probable", "weather_factor": 1.007, "weather_status": "available", "wrc_plus_status": "unavailable_from_source"}, "formula_spec": {"away_field_run_factor": 1.0, "bullpen_elasticity": 0.069018, "configuration_hash": "3b7bd3de474b03054313a1806d79c06d8b472b811a4a764926d95f599482d236", "factor_bounds": {"bullpen_weakness": [0.5, 2.0], "offense": [0.7, 1.4], "park": [0.8, 1.3], "starter_weakness": [0.5, 2.0], "weather": [0.85, 1.2]}, "feature_schema_version": "v3", "formula_version": "mlb-analyst-poisson-trend-v0.3", "home_field_run_factor": 1.04, "league_runs_per_team_game": 4.5347, "league_starter_era": 4.2036, "league_strikeout_rate": 0.219, "league_walk_rate": 0.079, "offense_elasticity": 0.088237, "park_elasticity": 0.259048, "recent_half_life_games": 10.0, "recent_prior_strength_games": 12.0, "seed_method": "stable_hash", "simulation": {"extra_inning_home_probability_bounds": [0.5, 0.55], "seed": 42, "shared_environment_variance": 0.06, "simulations": 20000, "team_specific_variance": 0.12}, "starter_rate_prior_batters_faced": 60.0, "starter_recent_prior_innings": 20.0, "starter_recent_weight": 0.7, "starter_season_prior_innings": 40.0, "starter_season_weight": 0.3, "starter_weakness_elasticity": 0.281107, "strikeout_weight": 0.15, "uncertainty": {"base": 0.02, "bullpen_unavailable": 0.02, "lineup_projected": 0.015, "lineup_unavailable": 0.025, "maximum": 0.15, "minimum": 0.02, "missing_wrc_plus": 0.01, "missing_xfip": 0.01, "model_form": 0.01, "pitcher": 0.015, "rookie_starter": 0.03, "weather_unavailable": 0.01}, "walk_weight": 0.1, "weather_elasticity": 0.040295}, "historical_source_observation_times_verified": false, "market_type": "spread", "model_version": "measured-edge-margin-v3", "observed_at_utc": "2026-10-14T05:51:02.821322+00:00", "raw_probabilities": {"away": 0.64245, "home": 0.35755, "push": 0.0}, "replay_scope": "Exact features, formula and deterministic Monte Carlo seed inputs; independently calibrated sides are not a joint distribution.", "run_estimate": {"away_expected_runs": 3.714607, "configuration_hash": "3b7bd3de474b03054313a1806d79c06d8b472b811a4a764926d95f599482d236", "factors": {"away_bullpen_weakness_index": 0.754003, "away_field_run_factor": 1.0, "away_offense_index": 0.9425246552787943, "away_starter_weakness_index": 0.6865741944073087, "home_bullpen_weakness_index": 0.543735, "home_field_run_factor": 1.04, "home_offense_index": 0.8967492210167299, "home_starter_weakness_index": 0.5692565140693949, "park_factor": 1.023, "weather_factor": 1.007}, "feature_schema_version": "v3", "formula_version": "mlb-analyst-poisson-trend-v0.3", "home_expected_runs": 4.146812, "uncertainty": 0.042131, "uncertainty_components": {"base": 0.02, "lineup": 0.025, "missing_wrc_plus": 0.01, "missing_xfip": 0.01, "model_form": 0.01, "pitcher": 0.015, "starter_confirmation": 0.015}}, "schema": "mlb-margin-replay-v1", "served_probabilities": {"away": 0.597065, "home": 0.402935}, "snapshot_hash": "71ea2ab548587ace34fe4c5a4bddf026cee93a2c67ad034e7a0ee486b3304c9e", "sport": "MLB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>30161cd696be4aa1</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:02.821322Z</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00Z</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>401908032</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>MLB</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J57" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>-106</v>
+      </c>
+      <c r="M57" s="27" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="N57" s="28" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="O57" s="28" t="n">
+        <v>0.509489</v>
+      </c>
+      <c r="P57" s="28" t="n">
+        <v>0.042131</v>
+      </c>
+      <c r="Q57" s="28" t="n">
+        <v>-0.005074</v>
+      </c>
+      <c r="R57" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="S57" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="U57" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V57" s="24" t="n"/>
+      <c r="W57" s="26" t="n"/>
+      <c r="X57" s="26" t="n"/>
+      <c r="Y57" s="25" t="n"/>
+      <c r="Z57" s="26" t="n"/>
+      <c r="AA57" s="28" t="n"/>
+      <c r="AB57" s="28" t="n"/>
+      <c r="AC57" s="30" t="n"/>
+      <c r="AD57" s="24" t="n"/>
+      <c r="AE57" s="31" t="inlineStr">
+        <is>
+          <t>Measured Edge Totals: Trend Engine projected 3.71-4.15; raw selected-side p=0.5149, calibrated p=0.5095.</t>
+        </is>
+      </c>
+      <c r="AF57" s="31" t="inlineStr">
+        <is>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+        </is>
+      </c>
+      <c r="AG57" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH57" s="24" t="n"/>
+      <c r="AI57" s="31" t="n"/>
+      <c r="AJ57" s="31" t="n"/>
+      <c r="AK57" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL57" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM57" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN57" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO57" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-mil</t>
+        </is>
+      </c>
+      <c r="AQ57" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AR57" s="24" t="inlineStr">
+        <is>
+          <t>Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="AS57" s="24" t="inlineStr">
+        <is>
+          <t>mlb-lad</t>
+        </is>
+      </c>
+      <c r="AT57" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AU57" s="24" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="AV57" s="24" t="n"/>
+      <c r="AW57" s="24" t="n"/>
+      <c r="AX57" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY57" s="24" t="n"/>
+      <c r="AZ57" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA57" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BB57" s="24" t="inlineStr">
+        <is>
+          <t>flat_probability_shrinkage_toward_half</t>
+        </is>
+      </c>
+      <c r="BC57" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-totals-v3</t>
+        </is>
+      </c>
+      <c r="BD57" s="24" t="inlineStr">
+        <is>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+        </is>
+      </c>
+      <c r="BE57" s="24" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF57" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG57" s="24" t="inlineStr">
+        <is>
+          <t>measured-edge-paired-v1</t>
+        </is>
+      </c>
+      <c r="BH57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:02.821322Z</t>
+        </is>
+      </c>
+      <c r="BI57" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ57" s="25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BK57" s="26" t="n">
+        <v>-106</v>
+      </c>
+      <c r="BL57" s="27" t="n">
+        <v>1.943396</v>
+      </c>
+      <c r="BM57" s="28" t="n">
+        <v>0.514563</v>
+      </c>
+      <c r="BN57" s="28" t="n">
+        <v>0.5124379999999999</v>
+      </c>
+      <c r="BO57" s="28" t="n"/>
+      <c r="BP57" s="25" t="n"/>
+      <c r="BQ57" s="27" t="n"/>
+      <c r="BR57" s="28" t="n"/>
+      <c r="BS57" s="28" t="n"/>
+      <c r="BT57" s="28" t="n"/>
+      <c r="BU57" s="25" t="n"/>
+      <c r="BV57" s="29" t="n"/>
+      <c r="BW57" s="24" t="n"/>
+      <c r="BX57" s="30" t="n"/>
+      <c r="BY57" s="27" t="n"/>
+      <c r="BZ57" s="24" t="n"/>
+      <c r="CA57" s="31" t="n"/>
+      <c r="CB57" s="24" t="n"/>
+      <c r="CC57" s="24" t="n"/>
+      <c r="CD57" s="24" t="n"/>
+      <c r="CE57" s="24" t="n"/>
+      <c r="CF57" s="24" t="n"/>
+      <c r="CG57" s="24" t="n"/>
+      <c r="CH57" s="24" t="n"/>
+      <c r="CI57" s="24" t="n"/>
+      <c r="CJ57" s="24" t="n"/>
+      <c r="CK57" s="24" t="n"/>
+      <c r="CL57" s="24" t="n"/>
+      <c r="CM57" s="24" t="n"/>
+      <c r="CN57" s="24" t="n"/>
+      <c r="CO57" s="24" t="n"/>
+      <c r="CP57" s="24" t="n"/>
+      <c r="CQ57" s="24" t="n"/>
+      <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT57" s="24" t="inlineStr">
+        <is>
+          <t>a9b23362b31654324ebb68d50a78c7a7cbb34dedfe01df9a0d6220e66c25ca47</t>
+        </is>
+      </c>
+      <c r="CU57" s="24" t="inlineStr">
+        <is>
+          <t>7da9fbc6da4044536749c6fcd9abae7c13da55057708570036207f0597844565</t>
+        </is>
+      </c>
+      <c r="CV57" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\model.yaml</t>
+        </is>
+      </c>
+      <c r="CW57" s="24" t="inlineStr">
+        <is>
+          <t>1dad20b56ac0a94181b31c5f71abe66cc0ee1acd8c8792d0aacf42b7a6fc32e6</t>
+        </is>
+      </c>
+      <c r="CX57" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\models\measured-edge-totals-v3.json</t>
+        </is>
+      </c>
+      <c r="CY57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:51:02.821322Z</t>
+        </is>
+      </c>
+      <c r="CZ57" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="DA57" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="DB57" s="24" t="inlineStr">
+        <is>
+          <t>decision_time_executable_quote</t>
+        </is>
+      </c>
+      <c r="DC57" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DD57" s="24" t="inlineStr">
+        <is>
+          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
+        </is>
+      </c>
+      <c r="DE57" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\data\market_odds_snapshots.jsonl</t>
+        </is>
+      </c>
+      <c r="DF57" s="24" t="inlineStr">
+        <is>
+          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
+        </is>
+      </c>
+      <c r="DG57" s="24" t="inlineStr">
+        <is>
+          <t>live_forecast</t>
+        </is>
+      </c>
+      <c r="DH57" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DI57" s="24" t="inlineStr">
+        <is>
+          <t>0.509489</t>
+        </is>
+      </c>
+      <c r="DJ57" s="24" t="inlineStr">
+        <is>
+          <t>0.5145631067961165</t>
+        </is>
+      </c>
+      <c r="DK57" s="24" t="inlineStr">
+        <is>
+          <t>0.509489</t>
+        </is>
+      </c>
+      <c r="DL57" s="24" t="n"/>
+      <c r="DM57" s="24" t="n"/>
+      <c r="DN57" s="24" t="n"/>
+      <c r="DO57" s="24" t="n"/>
+      <c r="DP57" s="24" t="n"/>
+      <c r="DQ57" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/mlb/flat.xlsx
+++ b/data/sports/mlb/flat.xlsx
@@ -21270,12 +21270,12 @@
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="24" t="inlineStr">
         <is>
-          <t>a44524dfbbab41b3</t>
+          <t>5cd33260c1524be4</t>
         </is>
       </c>
       <c r="B54" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:50:02.772612Z</t>
+          <t>2026-10-14T22:43:41.739454Z</t>
         </is>
       </c>
       <c r="C54" s="24" t="inlineStr">
@@ -21329,11 +21329,11 @@
         <v>0.619772</v>
       </c>
       <c r="O54" s="28" t="n">
-        <v>0.50234</v>
+        <v>0.502414</v>
       </c>
       <c r="P54" s="28" t="n"/>
       <c r="Q54" s="28" t="n">
-        <v>-0.117432</v>
+        <v>-0.117358</v>
       </c>
       <c r="R54" s="26" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
       <c r="AD54" s="24" t="n"/>
       <c r="AE54" s="31" t="inlineStr">
         <is>
-          <t>Learned LR call at threshold 0.6197; executable ask 0.6200 (aec-mlb-mil-lad-2026-10-14); model edge vs ask -0.1177.</t>
+          <t>Learned LR call at threshold 0.6197; executable ask 0.6200 (aec-mlb-mil-lad-2026-10-14); model edge vs ask -0.1176.</t>
         </is>
       </c>
       <c r="AF54" s="31" t="inlineStr">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="BE54" s="24" t="inlineStr">
         <is>
-          <t>73d276b25a216730</t>
+          <t>cbb2ef5926c7e580</t>
         </is>
       </c>
       <c r="BF54" s="24" t="inlineStr">
@@ -21481,7 +21481,7 @@
       </c>
       <c r="BH54" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T04:36:44.504334Z</t>
+          <t>2026-10-14T22:06:20.196594Z</t>
         </is>
       </c>
       <c r="BI54" s="24" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="CF54" s="24" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1.006</t>
         </is>
       </c>
       <c r="CG54" s="24" t="n"/>
@@ -21561,7 +21561,7 @@
       <c r="CQ54" s="24" t="n"/>
       <c r="CR54" s="24" t="inlineStr">
         <is>
-          <t>0.50234</t>
+          <t>0.502414</t>
         </is>
       </c>
       <c r="CS54" s="24" t="inlineStr">
@@ -21576,7 +21576,7 @@
       <c r="CX54" s="24" t="n"/>
       <c r="CY54" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T04:36:44.504334Z</t>
+          <t>2026-10-14T22:06:20.196594Z</t>
         </is>
       </c>
       <c r="CZ54" s="24" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="DD54" s="24" t="inlineStr">
         <is>
-          <t>1fddf5b0fa54c67a6f9ca44ef3359bb6fbb9693c751441a660d3e4e2944a3dbf</t>
+          <t>a2cd012d37cdf7ed49c59f019e4b9f4c663fef200157be5ccbcb6673c2099108</t>
         </is>
       </c>
       <c r="DE54" s="24" t="inlineStr">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="DF54" s="24" t="inlineStr">
         <is>
-          <t>1fddf5b0fa54c67a6f9ca44ef3359bb6fbb9693c751441a660d3e4e2944a3dbf</t>
+          <t>a2cd012d37cdf7ed49c59f019e4b9f4c663fef200157be5ccbcb6673c2099108</t>
         </is>
       </c>
       <c r="DG54" s="24" t="n"/>
@@ -21626,19 +21626,19 @@
       <c r="DP54" s="24" t="n"/>
       <c r="DQ54" s="24" t="inlineStr">
         <is>
-          <t>{"adjustment": {"applied": false, "method": "identity", "reason": "not_applicable"}, "artifact": {"artifact_hash": "3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8", "market_models": {"moneyline": {"coefficients": [3.0404972651, -0.0248808023, -0.9016764146, -0.2981045997, -0.0190272663, 0.1519919276], "confidence_threshold": 0.61966524, "feature_names": ["elo_probability", "trend_gap", "park_factor", "weather_factor", "starter_era_gap", "bullpen_weakness_gap"], "intercept": -0.2831037846, "positive_class": "home"}}, "method": "logistic_regression", "model_version": "mlb-elo-trend-lr-v8", "qualification": {"brier_score": 0.246354, "called_rate": 0.106398, "calls": 148, "failures": ["validation Brier regressed vs incumbent v7 feature set (0.24702 vs 0.24655) even though locked-holdout metrics clear the bar (0.6081 hit rate, 148 calls) -- disqualified under docs/AGENTS.md's promotion rule (a validation regression is not overridable by a good holdout number, since doing so is exactly 'peeking at holdout'). See qualification.validation_regression_note and training.promotion_rationale for the real numbers and the operator-directed override reasoning."], "framework": "locked_complete_date_60_20_20", "hit_rate": 0.608108, "hits": 90, "locked_holdout": true, "market_type": "moneyline", "meets_primary_holdout_metrics": true, "minimum_calls": 50, "minimum_hit_rate": 0.6, "qualification_eligible": true, "qualified": false, "sample_size": 1391, "training_data_note": "starter_era_gap depends on data/mlb_statsapi/game_snapshots.jsonl, kept current as of this artifact's build by cli.py's daily _capture_mlb_starter_snapshots step (added 2026-08-04, same day as this artifact) -- verify that capture is still running before trusting this feature live.", "units_at_minus_110": 23.818182, "validation_brier_score": 0.24702, "validation_brier_score_vs_incumbent": 0.00047, "validation_regression_note": "Validation Brier is WORSE than v7's incumbent feature set (0.24702 vs v7's 0.24655) while locked-holdout is better (0.24635 vs v7's 0.24763). This is the exact 'peek at holdout' pattern docs/AGENTS.md's promotion rule exists to catch -- promoted anyway by explicit operator directive 2026-08-04, not because it cleared this project's own automatic promotion bar. See training.promotion_rationale."}, "schema_version": "1", "sport": "mlb", "training": {"coefficient_fit": {"end": "2025-07-22", "observations": 3814, "start": "2024-04-06"}, "locked_holdout": {"end": "2026-07-29", "observations": 1391, "start": "2026-04-11"}, "market_inputs_used": false, "promotion_rationale": "Operator-directed promotion, 2026-08-04. Real walk-forward ablation (build_walk_forward_rows + chronological_split, matching v7's own methodology, self-consistency-verified by reproducing v7's exact stored holdout numbers before this comparison) replaced pitcher_era_gap (team-level rolling runs-allowed) with starter_era_gap (real per-starter rolling ERA from mlb_statsapi boxscore history, features/starter_history.py) -- the 'different functional form' docs/MODEL_IMPROVEMENTS.md's 'Rank-1 tested honestly' section flagged as worth trying after the additive form (adding starter_era_gap alongside pitcher_era_gap) showed the same validation/holdout disagreement tested 2026-08-02. Coefficient sign is correct (worse starter ERA -&gt; lower home win probability) in both the additive and replacement forms. Real numbers: locked-holdout hit_rate 0.6081 (148 calls, 90 hits) vs v7's +0.6242-threshold 0.6194. Not a clean automatic pass -- see qualification.validation_regression_note.", "threshold_selection": {"end": "2026-04-10", "observations": 1082, "start": "2025-07-23"}, "threshold_source": "validation cohort; never locked holdout", "walk_forward_features": true}}, "artifact_hash": "3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8", "base_home_probability": 0.5023398740151511, "event_id": "401908032", "event_start_utc": "2026-10-15T00:00:00+00:00", "features": {"bullpen_weakness_gap": -0.210268, "elo_probability": 0.5032338966034758, "park_factor": 1.023, "starter_era_gap": -0.4205, "trend_gap": -0.359572, "weather_factor": 1.007}, "historical_source_observation_times_verified": false, "model_version": "mlb-elo-trend-lr-v8", "observed_at_utc": "2026-10-14T05:50:02.772612+00:00", "schema": "learned-moneyline-replay-v1", "served_home_probability": 0.5023398740151511, "snapshot_hash": "712ab046697ae848ddeed982a7dd1b3fea62e3f96ea1498c3534a5359ec6b5a0"}</t>
+          <t>{"adjustment": {"applied": false, "method": "identity", "reason": "not_applicable"}, "artifact": {"artifact_hash": "3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8", "market_models": {"moneyline": {"coefficients": [3.0404972651, -0.0248808023, -0.9016764146, -0.2981045997, -0.0190272663, 0.1519919276], "confidence_threshold": 0.61966524, "feature_names": ["elo_probability", "trend_gap", "park_factor", "weather_factor", "starter_era_gap", "bullpen_weakness_gap"], "intercept": -0.2831037846, "positive_class": "home"}}, "method": "logistic_regression", "model_version": "mlb-elo-trend-lr-v8", "qualification": {"brier_score": 0.246354, "called_rate": 0.106398, "calls": 148, "failures": ["validation Brier regressed vs incumbent v7 feature set (0.24702 vs 0.24655) even though locked-holdout metrics clear the bar (0.6081 hit rate, 148 calls) -- disqualified under docs/AGENTS.md's promotion rule (a validation regression is not overridable by a good holdout number, since doing so is exactly 'peeking at holdout'). See qualification.validation_regression_note and training.promotion_rationale for the real numbers and the operator-directed override reasoning."], "framework": "locked_complete_date_60_20_20", "hit_rate": 0.608108, "hits": 90, "locked_holdout": true, "market_type": "moneyline", "meets_primary_holdout_metrics": true, "minimum_calls": 50, "minimum_hit_rate": 0.6, "qualification_eligible": true, "qualified": false, "sample_size": 1391, "training_data_note": "starter_era_gap depends on data/mlb_statsapi/game_snapshots.jsonl, kept current as of this artifact's build by cli.py's daily _capture_mlb_starter_snapshots step (added 2026-08-04, same day as this artifact) -- verify that capture is still running before trusting this feature live.", "units_at_minus_110": 23.818182, "validation_brier_score": 0.24702, "validation_brier_score_vs_incumbent": 0.00047, "validation_regression_note": "Validation Brier is WORSE than v7's incumbent feature set (0.24702 vs v7's 0.24655) while locked-holdout is better (0.24635 vs v7's 0.24763). This is the exact 'peek at holdout' pattern docs/AGENTS.md's promotion rule exists to catch -- promoted anyway by explicit operator directive 2026-08-04, not because it cleared this project's own automatic promotion bar. See training.promotion_rationale."}, "schema_version": "1", "sport": "mlb", "training": {"coefficient_fit": {"end": "2025-07-22", "observations": 3814, "start": "2024-04-06"}, "locked_holdout": {"end": "2026-07-29", "observations": 1391, "start": "2026-04-11"}, "market_inputs_used": false, "promotion_rationale": "Operator-directed promotion, 2026-08-04. Real walk-forward ablation (build_walk_forward_rows + chronological_split, matching v7's own methodology, self-consistency-verified by reproducing v7's exact stored holdout numbers before this comparison) replaced pitcher_era_gap (team-level rolling runs-allowed) with starter_era_gap (real per-starter rolling ERA from mlb_statsapi boxscore history, features/starter_history.py) -- the 'different functional form' docs/MODEL_IMPROVEMENTS.md's 'Rank-1 tested honestly' section flagged as worth trying after the additive form (adding starter_era_gap alongside pitcher_era_gap) showed the same validation/holdout disagreement tested 2026-08-02. Coefficient sign is correct (worse starter ERA -&gt; lower home win probability) in both the additive and replacement forms. Real numbers: locked-holdout hit_rate 0.6081 (148 calls, 90 hits) vs v7's +0.6242-threshold 0.6194. Not a clean automatic pass -- see qualification.validation_regression_note.", "threshold_selection": {"end": "2026-04-10", "observations": 1082, "start": "2025-07-23"}, "threshold_source": "validation cohort; never locked holdout", "walk_forward_features": true}}, "artifact_hash": "3b345499bd6bad9bcf65367a07fe0c668fb5817d4f016a0a865c01d9212fdeb8", "base_home_probability": 0.5024143984804157, "event_id": "401908032", "event_start_utc": "2026-10-15T00:00:00+00:00", "features": {"bullpen_weakness_gap": -0.210268, "elo_probability": 0.5032338966034758, "park_factor": 1.023, "starter_era_gap": -0.4205, "trend_gap": -0.359572, "weather_factor": 1.006}, "historical_source_observation_times_verified": false, "model_version": "mlb-elo-trend-lr-v8", "observed_at_utc": "2026-10-14T22:43:41.739454+00:00", "schema": "learned-moneyline-replay-v1", "served_home_probability": 0.5024143984804157, "snapshot_hash": "ff6d1a2e48fb6a1704a9c364a2569eeb67a8d80ca28104c5e63598afe835ea5d"}</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="24" t="inlineStr">
         <is>
-          <t>2639f8d3ead94bd9</t>
+          <t>b5297f8f1b4f4ecf</t>
         </is>
       </c>
       <c r="B55" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:03.681835Z</t>
+          <t>2026-10-14T22:45:17.075038Z</t>
         </is>
       </c>
       <c r="C55" s="24" t="inlineStr">
@@ -21668,16 +21668,16 @@
       </c>
       <c r="H55" s="24" t="inlineStr">
         <is>
-          <t>nrfi</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I55" s="24" t="inlineStr">
         <is>
-          <t>yrfi</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J55" s="25" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
@@ -21685,32 +21685,32 @@
         </is>
       </c>
       <c r="L55" s="26" t="n">
-        <v>117</v>
+        <v>-133</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>2.17</v>
+        <v>1.75188</v>
       </c>
       <c r="N55" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.570815</v>
       </c>
       <c r="O55" s="28" t="n">
-        <v>0.4812</v>
+        <v>0.599041</v>
       </c>
       <c r="P55" s="28" t="n">
-        <v>0.04</v>
+        <v>0.042131</v>
       </c>
       <c r="Q55" s="28" t="n">
-        <v>0.020371</v>
+        <v>0.028226</v>
       </c>
       <c r="R55" s="26" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S55" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T55" s="24" t="inlineStr">
         <is>
-          <t>mlb-nrfi-v4</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="U55" s="24" t="inlineStr">
@@ -21729,12 +21729,12 @@
       <c r="AD55" s="24" t="n"/>
       <c r="AE55" s="31" t="inlineStr">
         <is>
-          <t>MLB 1st Inning YRFI: p=0.481 vs ask 0.460 (astatc-mlb-mil-lad-2026-10-14-yrfi; edge +0.0212) (mlb-nrfi-v4, 4272 training games)</t>
+          <t>Measured Edge Margin: Trend Engine projected 3.71-4.15; raw selected-side p=0.6453, calibrated p=0.5990.</t>
         </is>
       </c>
       <c r="AF55" s="31" t="inlineStr">
         <is>
-          <t>1st inning variance, leadoff home run risk</t>
+          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
         </is>
       </c>
       <c r="AG55" s="24" t="inlineStr">
@@ -21808,47 +21808,47 @@
       <c r="AY55" s="24" t="n"/>
       <c r="AZ55" s="24" t="inlineStr">
         <is>
-          <t>shadow_qualified</t>
+          <t>research</t>
         </is>
       </c>
       <c r="BA55" s="24" t="inlineStr">
         <is>
-          <t>cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BB55" s="24" t="inlineStr">
         <is>
-          <t>half_inning_interaction</t>
+          <t>flat_probability_shrinkage_toward_half</t>
         </is>
       </c>
       <c r="BC55" s="24" t="inlineStr">
         <is>
-          <t>mlb-nrfi-v4</t>
+          <t>measured-edge-margin-v3</t>
         </is>
       </c>
       <c r="BD55" s="24" t="inlineStr">
         <is>
-          <t>cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff</t>
+          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
         </is>
       </c>
       <c r="BE55" s="24" t="inlineStr">
         <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="BF55" s="24" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BF55" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="BG55" s="24" t="inlineStr">
         <is>
-          <t>scalar-artifact-replay-v1</t>
+          <t>measured-edge-paired-v1</t>
         </is>
       </c>
       <c r="BH55" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T04:36:04.233595Z</t>
+          <t>2026-10-14T22:45:17.075038Z</t>
         </is>
       </c>
       <c r="BI55" s="24" t="inlineStr">
@@ -21857,18 +21857,20 @@
         </is>
       </c>
       <c r="BJ55" s="25" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="BK55" s="26" t="n">
-        <v>117</v>
+        <v>-133</v>
       </c>
       <c r="BL55" s="27" t="n">
-        <v>2.17</v>
+        <v>1.75188</v>
       </c>
       <c r="BM55" s="28" t="n">
-        <v>0.460829</v>
-      </c>
-      <c r="BN55" s="28" t="n"/>
+        <v>0.570815</v>
+      </c>
+      <c r="BN55" s="28" t="n">
+        <v>0.567164</v>
+      </c>
       <c r="BO55" s="28" t="n"/>
       <c r="BP55" s="25" t="n"/>
       <c r="BQ55" s="27" t="n"/>
@@ -21904,14 +21906,34 @@
           <t>True</t>
         </is>
       </c>
-      <c r="CT55" s="24" t="n"/>
-      <c r="CU55" s="24" t="n"/>
-      <c r="CV55" s="24" t="n"/>
-      <c r="CW55" s="24" t="n"/>
-      <c r="CX55" s="24" t="n"/>
+      <c r="CT55" s="24" t="inlineStr">
+        <is>
+          <t>0a506009b4e11c51583810a98869537ebd66a115c617e44359cd8f40332d6289</t>
+        </is>
+      </c>
+      <c r="CU55" s="24" t="inlineStr">
+        <is>
+          <t>427410a694833f4215ff3323c28ab9cb10bb9be8b193b12188d3c6fc38ef62ba</t>
+        </is>
+      </c>
+      <c r="CV55" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\model.yaml</t>
+        </is>
+      </c>
+      <c r="CW55" s="24" t="inlineStr">
+        <is>
+          <t>1ac81f4be213944a7cce95cbe9a52520e640a9cc5ea1424409aeda60b059f716</t>
+        </is>
+      </c>
+      <c r="CX55" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\models\measured-edge-margin-v3.json</t>
+        </is>
+      </c>
       <c r="CY55" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T04:36:04.233595Z</t>
+          <t>2026-10-14T22:45:17.075038Z</t>
         </is>
       </c>
       <c r="CZ55" s="24" t="inlineStr">
@@ -21936,24 +21958,44 @@
       </c>
       <c r="DD55" s="24" t="inlineStr">
         <is>
-          <t>617a759a29e9d2ea3d7f9c2c21680515363c9c2a804f3659ea7474b48ecc1ca8</t>
+          <t>9f538f9f74c2493fe8e50ec1ee0cff154c1a486233d037f8fec55a1d41f380a5</t>
         </is>
       </c>
       <c r="DE55" s="24" t="inlineStr">
         <is>
-          <t>E:\model-prediction\data\odds\mlb\2026-10-14\polymarket_snapshots.jsonl</t>
+          <t>E:\model-prediction\data\market_odds_snapshots.jsonl</t>
         </is>
       </c>
       <c r="DF55" s="24" t="inlineStr">
         <is>
-          <t>617a759a29e9d2ea3d7f9c2c21680515363c9c2a804f3659ea7474b48ecc1ca8</t>
-        </is>
-      </c>
-      <c r="DG55" s="24" t="n"/>
-      <c r="DH55" s="24" t="n"/>
-      <c r="DI55" s="24" t="n"/>
-      <c r="DJ55" s="24" t="n"/>
-      <c r="DK55" s="24" t="n"/>
+          <t>9f538f9f74c2493fe8e50ec1ee0cff154c1a486233d037f8fec55a1d41f380a5</t>
+        </is>
+      </c>
+      <c r="DG55" s="24" t="inlineStr">
+        <is>
+          <t>live_forecast</t>
+        </is>
+      </c>
+      <c r="DH55" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="DI55" s="24" t="inlineStr">
+        <is>
+          <t>0.599041</t>
+        </is>
+      </c>
+      <c r="DJ55" s="24" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="DK55" s="24" t="inlineStr">
+        <is>
+          <t>0.599041</t>
+        </is>
+      </c>
       <c r="DL55" s="24" t="n"/>
       <c r="DM55" s="24" t="n"/>
       <c r="DN55" s="24" t="n"/>
@@ -21961,19 +22003,19 @@
       <c r="DP55" s="24" t="n"/>
       <c r="DQ55" s="24" t="inlineStr">
         <is>
-          <t>{"artifact": {"C": 1.0, "artifact_hash": "cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff", "coef_away": [-0.15092599233710682, 0.33375332491407694, 0.052641650764709516, 0.012200963333336163, -0.044124086984268916, -0.18338539828154118, -0.011069775160598767, -0.07334888990228486, 0.2843164406703071, -0.016022382971498418, -0.42919391686573305, -0.13322539735898248], "coef_home": [-0.056762054222791236, 0.1634913765713207, -0.12677479939259476, -0.10980892029364075, 0.0675840668410901, -0.2155237746431725, -0.0015823333282579347, -0.0017682883771573481, 0.30292713155931383, -0.26515719099464424, -0.24182390473213353, 0.146893598319729], "feature_names": ["top3_composite", "starter_opp_1st_runs", "starter_fip", "starter_k_pct", "starter_bb_pct", "park_1st_runs", "top3_same_hand_share", "team_1st_scored", "top3_park_interaction", "whiff_power_interaction", "starter_park_interaction", "fip_k_ratio"], "fit_n_games": 4272, "intercept_away": 1.0122829388370416, "intercept_home": 0.8796220049130925, "league": "MLB", "market_type": "nrfi", "method": "half_inning_interaction", "model_version": "mlb-nrfi-v4", "note": "Production-qualified MLB first-inning interaction component model replacing mlb-nrfi-v3.", "positive_class": "nrfi", "qualification": {"binary_accuracy": 0.5485, "calibration_ece": 0.021121, "framework": "half_inning_interaction_holdout", "holdout_brier_score": 0.247866, "holdout_log_loss": 0.688855, "locked_holdout": true, "note": "Two-half-inning decomposed model with non-linear interaction features (park, strikeout-whiff, platoon hand alignment) evaluated on 1,424 locked holdout test games.", "qualified": true, "sample_size": 1424, "status": "qualified"}, "scaler_mean_away": [0.10693852528089877, 0.5160531601123584, 3.887999765917613, 0.22160819288389438, 0.07721193820224699, 1.0095550561797733, 0.5512290262172258, 0.4530846910112346, 0.10797593867883881, 0.0832338340753744, 0.522421086896067, 12.74853166149649], "scaler_mean_home": [0.10687735955056178, 0.4668664091760332, 3.880392556179783, 0.22145009363295864, 0.07637907303370803, 1.0095550561797733, 0.5500498361423202, 0.5488433520599267, 0.10794226697635774, 0.08320755243679794, 0.47126779163623655, 12.714614928114717], "scaler_scale_away": [0.0048171779396999235, 0.12136652246642901, 1.0539601780342398, 0.05165113643883803, 0.02673985154876719, 0.09232773263326173, 0.10967171480498189, 0.0982166066212668, 0.01119895692211545, 0.0065842717464252515, 0.13841807595534883, 5.363640846622892], "scaler_scale_home": [0.0049927679114434974, 0.11700796360197874, 1.0206033876941032, 0.052293646761000234, 0.02791997429590162, 0.09232773263326173, 0.11057352848346676, 0.10479111868852325, 0.011525124767030699, 0.006780208072838942, 0.12566593459901798, 5.16406006135981], "schema_version": "2", "sport": "mlb"}, "artifact_hash": "cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff", "engine_source_sha256": "0d1788de892d97e815079a85f389a8dcfd16276fa807f5d446a8a943717fd8da", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "features": {"away_starter_bb_pct": 0.068, "away_starter_days_rest": 6.0, "away_starter_fip": 4.011, "away_starter_k_pct": 0.2039, "away_starter_opp_1st_runs": 0.3185, "away_starter_starts": 3.2958, "away_team_1st_allowed_away": 0.3905, "away_team_1st_scored_away": 0.4186, "away_top3_composite": 0.10642, "home_starter_bb_pct": 0.1018, "home_starter_days_rest": 6.0, "home_starter_fip": 2.288, "home_starter_k_pct": 0.3219, "home_starter_opp_1st_runs": 0.3549, "home_starter_starts": 3.7136, "home_team_1st_allowed_home": 0.5969, "home_team_1st_scored_home": 0.7213, "home_top3_composite": 0.11451, "park_1st_runs": 1.2151}, "historical_source_observation_times_verified": false, "inference_inputs": {}, "model_version": "mlb-nrfi-v4", "observed_at_utc": "2026-10-14T05:51:03.681835+00:00", "replay_scope": "Exact final classifier/distribution inputs and artifact. Upstream historical feature construction not certified.", "schema": "scalar-artifact-replay-v1", "snapshot_hash": "e58f5355b1efd31ad2cf319a5a51a26cf1b3bd241959f525dbcbac1d16bed90b"}</t>
+          <t>{"artifact": {"artifact_hash": "dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c", "base_score_model_version": "mlb-analyst-poisson-trend-v0.3", "calibration_method": "flat_probability_shrinkage_toward_half", "calibration_note": "Rebuilt against mlb-analyst-poisson-trend-v0.3's refit elasticities (scripts/mlb_elasticity_refit.py) and fresh game data (scripts/mlb_measured_edge_calibrate.py). Primary fit (this artifact's top-level scale/offset) is OLS of the rebuilt formula's raw simulated cover probability against real game outcomes over 290 games from data/historical/mlb_market_lines_reconstructed.jsonl -- ESPN's own postgame pickcenter reconstruction, hard-labeled timestamp_valid=False by ingest.py::reconstruct_mlb_markets; diagnostic only, NOT real historical Polymarket lines (correcting v1's calibration_note, which mischaracterized this same data source). Correlation with real outcomes: 0.208. Flat -110 diagnostic: {'picks': 285, 'hit_rate': 0.6, 'units': 41.45}. Real-market (genuine captured Polymarket BBO) corroboration: 65 games, scale=0.7458, offset=0.1271, correlation=0.2197, flat -110: {'picks': 63, 'hit_rate': 0.6349, 'units': 13.36}.", "calibration_version": "measured-edge-margin-v3", "calibration_windows": {"diagnostic": {"correlation": 0.208, "flat_110_diagnostic": {"hit_rate": 0.6, "picks": 285, "units": 41.45}, "games": 290, "offset": 0.1593, "scale": 0.6814}, "real_market": {"correlation": 0.2197, "flat_110_diagnostic": {"hit_rate": 0.6349, "picks": 63, "units": 13.36}, "games": 65, "offset": 0.1271, "scale": 0.7458}}, "model_name": "Measured Edge Margin", "model_version": "measured-edge-margin-v3", "offset": 0.1593, "scale": 0.6814, "trained_on_games": 290}, "artifact_hash": "dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c", "away_spread_line": 1.5, "code_sha256": "58bccd1bb97abfc14ea818deb7642e49ab5cbaa6126f4e3d79f33944ad129267", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "features": {"away_bullpen_status": "available", "away_bullpen_weakness": 0.754003, "away_form": {"losses": 1, "runs_allowed": [2, 3, 4, 1, 1, 4], "runs_scored": [3, 4, 3, 3, 2, 7], "status": "available", "wins": 5}, "away_starter": {"last_five_batters_faced": 103, "last_five_earned_runs": 4, "last_five_innings": 26.666666666666668, "last_five_strikeouts": 24, "last_five_walks": 9, "name": "Robert Gasser", "player_id": "4918251", "season_batters_faced": 480, "season_earned_runs": 48, "season_innings": 113.33333333333333, "season_strikeouts": 106, "season_walks": 36, "starts_before_game": 22, "status": "available", "throwing_hand": "Left", "xfip": null, "xfip_status": "unavailable_from_source"}, "away_team": "Milwaukee Brewers", "decision_timestamp_utc": "2026-10-14T22:00:00Z", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "feature_snapshot_hash": "8e92dfa43e87c1f01a1813f14db8b751b1bd318453875cd1fb62e01c40968685", "home_bullpen_status": "available", "home_bullpen_weakness": 0.543735, "home_form": {"losses": 3, "runs_allowed": [3, 3, 1, 1, 2, 7], "runs_scored": [5, 2, 3, 4, 1, 4], "status": "available", "wins": 3}, "home_starter": {"last_five_batters_faced": 83, "last_five_earned_runs": 3, "last_five_innings": 20.333333333333332, "last_five_strikeouts": 24, "last_five_walks": 9, "name": "Blake Snell", "player_id": "33748", "season_batters_faced": 192, "season_earned_runs": 10, "season_innings": 46.333333333333336, "season_strikeouts": 60, "season_walks": 21, "starts_before_game": 10, "status": "available", "throwing_hand": "Left", "xfip": null, "xfip_status": "unavailable_from_source"}, "home_team": "Los Angeles Dodgers", "lineup_status": "unavailable_from_source", "market_snapshot_hash": "9f538f9f74c2493fe8e50ec1ee0cff154c1a486233d037f8fec55a1d41f380a5", "park_factor": 1.023, "park_factor_status": "available", "source_snapshot_ids": ["94dc5da25fcd252b5380944173bad29abac80714493b315ab80a89d51be8d474", "702d171c7b929bb58fdedc6cd1825a94981d0224b2636e47d882a5bee740a62a", "6908715f637d10c428907e2214b6348ce7ab1f2103fe63ed3368c2139e70b7f3", "f1a7e31918b14d7624dbfd79cab472bc83bcbc72378dbf3017f6cb119f29cb6e", "cd3f9d3d1878bc5d0763fa220c7d747cc9c72ac8692a20d370c4a8aaa613db7b"], "starter_confirmed": false, "starter_status": "probable", "weather_factor": 1.006, "weather_status": "available", "wrc_plus_status": "unavailable_from_source"}, "formula_spec": {"away_field_run_factor": 1.0, "bullpen_elasticity": 0.069018, "configuration_hash": "3b7bd3de474b03054313a1806d79c06d8b472b811a4a764926d95f599482d236", "factor_bounds": {"bullpen_weakness": [0.5, 2.0], "offense": [0.7, 1.4], "park": [0.8, 1.3], "starter_weakness": [0.5, 2.0], "weather": [0.85, 1.2]}, "feature_schema_version": "v3", "formula_version": "mlb-analyst-poisson-trend-v0.3", "home_field_run_factor": 1.04, "league_runs_per_team_game": 4.5347, "league_starter_era": 4.2036, "league_strikeout_rate": 0.219, "league_walk_rate": 0.079, "offense_elasticity": 0.088237, "park_elasticity": 0.259048, "recent_half_life_games": 10.0, "recent_prior_strength_games": 12.0, "seed_method": "stable_hash", "simulation": {"extra_inning_home_probability_bounds": [0.5, 0.55], "seed": 42, "shared_environment_variance": 0.06, "simulations": 20000, "team_specific_variance": 0.12}, "starter_rate_prior_batters_faced": 60.0, "starter_recent_prior_innings": 20.0, "starter_recent_weight": 0.7, "starter_season_prior_innings": 40.0, "starter_season_weight": 0.3, "starter_weakness_elasticity": 0.281107, "strikeout_weight": 0.15, "uncertainty": {"base": 0.02, "bullpen_unavailable": 0.02, "lineup_projected": 0.015, "lineup_unavailable": 0.025, "maximum": 0.15, "minimum": 0.02, "missing_wrc_plus": 0.01, "missing_xfip": 0.01, "model_form": 0.01, "pitcher": 0.015, "rookie_starter": 0.03, "weather_unavailable": 0.01}, "walk_weight": 0.1, "weather_elasticity": 0.040295}, "historical_source_observation_times_verified": false, "market_type": "spread", "model_version": "measured-edge-margin-v3", "observed_at_utc": "2026-10-14T22:45:17.075038+00:00", "raw_probabilities": {"away": 0.64535, "home": 0.35465, "push": 0.0}, "replay_scope": "Exact features, formula and deterministic Monte Carlo seed inputs; independently calibrated sides are not a joint distribution.", "run_estimate": {"away_expected_runs": 3.714458, "configuration_hash": "3b7bd3de474b03054313a1806d79c06d8b472b811a4a764926d95f599482d236", "factors": {"away_bullpen_weakness_index": 0.754003, "away_field_run_factor": 1.0, "away_offense_index": 0.9425246552787943, "away_starter_weakness_index": 0.6865741944073087, "home_bullpen_weakness_index": 0.543735, "home_field_run_factor": 1.04, "home_offense_index": 0.8967492210167299, "home_starter_weakness_index": 0.5692565140693949, "park_factor": 1.023, "weather_factor": 1.006}, "feature_schema_version": "v3", "formula_version": "mlb-analyst-poisson-trend-v0.3", "home_expected_runs": 4.146646, "uncertainty": 0.042131, "uncertainty_components": {"base": 0.02, "lineup": 0.025, "missing_wrc_plus": 0.01, "missing_xfip": 0.01, "model_form": 0.01, "pitcher": 0.015, "starter_confirmation": 0.015}}, "schema": "mlb-margin-replay-v1", "served_probabilities": {"away": 0.599041, "home": 0.400959}, "snapshot_hash": "10bdab1a1ce7081723cffe6534decbec9aee5844833c2edc8d566dbe920446a9", "sport": "MLB"}</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="24" t="inlineStr">
         <is>
-          <t>2dbd181ed5c2485b</t>
+          <t>a4874c52ea7b4148</t>
         </is>
       </c>
       <c r="B56" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:02.821322Z</t>
+          <t>2026-10-14T22:45:17.075038Z</t>
         </is>
       </c>
       <c r="C56" s="24" t="inlineStr">
@@ -22003,16 +22045,16 @@
       </c>
       <c r="H56" s="24" t="inlineStr">
         <is>
-          <t>spread</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I56" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>under</t>
         </is>
       </c>
       <c r="J56" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="K56" s="24" t="inlineStr">
         <is>
@@ -22020,32 +22062,32 @@
         </is>
       </c>
       <c r="L56" s="26" t="n">
-        <v>-141</v>
+        <v>-115</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>1.70922</v>
+        <v>1.869565</v>
       </c>
       <c r="N56" s="28" t="n">
-        <v>0.585062</v>
+        <v>0.534884</v>
       </c>
       <c r="O56" s="28" t="n">
-        <v>0.597065</v>
+        <v>0.509601</v>
       </c>
       <c r="P56" s="28" t="n">
         <v>0.042131</v>
       </c>
       <c r="Q56" s="28" t="n">
-        <v>0.012003</v>
+        <v>-0.025283</v>
       </c>
       <c r="R56" s="26" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="S56" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v3</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="U56" s="24" t="inlineStr">
@@ -22064,7 +22106,7 @@
       <c r="AD56" s="24" t="n"/>
       <c r="AE56" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Margin: Trend Engine projected 3.71-4.15; raw selected-side p=0.6424, calibrated p=0.5971.</t>
+          <t>Measured Edge Totals: Trend Engine projected 3.71-4.15; raw selected-side p=0.5153, calibrated p=0.5096.</t>
         </is>
       </c>
       <c r="AF56" s="31" t="inlineStr">
@@ -22082,7 +22124,7 @@
       <c r="AJ56" s="31" t="n"/>
       <c r="AK56" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>paper_call</t>
         </is>
       </c>
       <c r="AL56" s="26" t="n">
@@ -22090,7 +22132,7 @@
       </c>
       <c r="AM56" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN56" s="24" t="inlineStr">
@@ -22100,7 +22142,7 @@
       </c>
       <c r="AO56" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP56" s="24" t="inlineStr">
@@ -22148,7 +22190,7 @@
       </c>
       <c r="BA56" s="24" t="inlineStr">
         <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BB56" s="24" t="inlineStr">
@@ -22158,12 +22200,12 @@
       </c>
       <c r="BC56" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-margin-v3</t>
+          <t>measured-edge-totals-v3</t>
         </is>
       </c>
       <c r="BD56" s="24" t="inlineStr">
         <is>
-          <t>dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c</t>
+          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
         </is>
       </c>
       <c r="BE56" s="24" t="inlineStr">
@@ -22183,7 +22225,7 @@
       </c>
       <c r="BH56" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:02.821322Z</t>
+          <t>2026-10-14T22:45:17.075038Z</t>
         </is>
       </c>
       <c r="BI56" s="24" t="inlineStr">
@@ -22192,19 +22234,19 @@
         </is>
       </c>
       <c r="BJ56" s="25" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="BK56" s="26" t="n">
-        <v>-141</v>
+        <v>-115</v>
       </c>
       <c r="BL56" s="27" t="n">
-        <v>1.70922</v>
+        <v>1.869565</v>
       </c>
       <c r="BM56" s="28" t="n">
-        <v>0.585062</v>
+        <v>0.534884</v>
       </c>
       <c r="BN56" s="28" t="n">
-        <v>0.58209</v>
+        <v>0.532338</v>
       </c>
       <c r="BO56" s="28" t="n"/>
       <c r="BP56" s="25" t="n"/>
@@ -22238,44 +22280,44 @@
       <c r="CR56" s="24" t="n"/>
       <c r="CS56" s="24" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT56" s="24" t="inlineStr">
+        <is>
+          <t>0a506009b4e11c51583810a98869537ebd66a115c617e44359cd8f40332d6289</t>
+        </is>
+      </c>
+      <c r="CU56" s="24" t="inlineStr">
+        <is>
+          <t>427410a694833f4215ff3323c28ab9cb10bb9be8b193b12188d3c6fc38ef62ba</t>
+        </is>
+      </c>
+      <c r="CV56" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\model.yaml</t>
+        </is>
+      </c>
+      <c r="CW56" s="24" t="inlineStr">
+        <is>
+          <t>1dad20b56ac0a94181b31c5f71abe66cc0ee1acd8c8792d0aacf42b7a6fc32e6</t>
+        </is>
+      </c>
+      <c r="CX56" s="24" t="inlineStr">
+        <is>
+          <t>E:\model-prediction\config\models\measured-edge-totals-v3.json</t>
+        </is>
+      </c>
+      <c r="CY56" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:45:17.075038Z</t>
+        </is>
+      </c>
+      <c r="CZ56" s="24" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="CT56" s="24" t="inlineStr">
-        <is>
-          <t>a9b23362b31654324ebb68d50a78c7a7cbb34dedfe01df9a0d6220e66c25ca47</t>
-        </is>
-      </c>
-      <c r="CU56" s="24" t="inlineStr">
-        <is>
-          <t>7da9fbc6da4044536749c6fcd9abae7c13da55057708570036207f0597844565</t>
-        </is>
-      </c>
-      <c r="CV56" s="24" t="inlineStr">
-        <is>
-          <t>E:\model-prediction\config\model.yaml</t>
-        </is>
-      </c>
-      <c r="CW56" s="24" t="inlineStr">
-        <is>
-          <t>1ac81f4be213944a7cce95cbe9a52520e640a9cc5ea1424409aeda60b059f716</t>
-        </is>
-      </c>
-      <c r="CX56" s="24" t="inlineStr">
-        <is>
-          <t>E:\model-prediction\config\models\measured-edge-margin-v3.json</t>
-        </is>
-      </c>
-      <c r="CY56" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-14T05:51:02.821322Z</t>
-        </is>
-      </c>
-      <c r="CZ56" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
       <c r="DA56" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -22293,7 +22335,7 @@
       </c>
       <c r="DD56" s="24" t="inlineStr">
         <is>
-          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
+          <t>9f538f9f74c2493fe8e50ec1ee0cff154c1a486233d037f8fec55a1d41f380a5</t>
         </is>
       </c>
       <c r="DE56" s="24" t="inlineStr">
@@ -22303,7 +22345,7 @@
       </c>
       <c r="DF56" s="24" t="inlineStr">
         <is>
-          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
+          <t>9f538f9f74c2493fe8e50ec1ee0cff154c1a486233d037f8fec55a1d41f380a5</t>
         </is>
       </c>
       <c r="DG56" s="24" t="inlineStr">
@@ -22318,17 +22360,17 @@
       </c>
       <c r="DI56" s="24" t="inlineStr">
         <is>
-          <t>0.597065</t>
+          <t>0.509601</t>
         </is>
       </c>
       <c r="DJ56" s="24" t="inlineStr">
         <is>
-          <t>0.5850622406639003</t>
+          <t>0.5348837209302326</t>
         </is>
       </c>
       <c r="DK56" s="24" t="inlineStr">
         <is>
-          <t>0.597065</t>
+          <t>0.509601</t>
         </is>
       </c>
       <c r="DL56" s="24" t="n"/>
@@ -22336,21 +22378,17 @@
       <c r="DN56" s="24" t="n"/>
       <c r="DO56" s="24" t="n"/>
       <c r="DP56" s="24" t="n"/>
-      <c r="DQ56" s="24" t="inlineStr">
-        <is>
-          <t>{"artifact": {"artifact_hash": "dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c", "base_score_model_version": "mlb-analyst-poisson-trend-v0.3", "calibration_method": "flat_probability_shrinkage_toward_half", "calibration_note": "Rebuilt against mlb-analyst-poisson-trend-v0.3's refit elasticities (scripts/mlb_elasticity_refit.py) and fresh game data (scripts/mlb_measured_edge_calibrate.py). Primary fit (this artifact's top-level scale/offset) is OLS of the rebuilt formula's raw simulated cover probability against real game outcomes over 290 games from data/historical/mlb_market_lines_reconstructed.jsonl -- ESPN's own postgame pickcenter reconstruction, hard-labeled timestamp_valid=False by ingest.py::reconstruct_mlb_markets; diagnostic only, NOT real historical Polymarket lines (correcting v1's calibration_note, which mischaracterized this same data source). Correlation with real outcomes: 0.208. Flat -110 diagnostic: {'picks': 285, 'hit_rate': 0.6, 'units': 41.45}. Real-market (genuine captured Polymarket BBO) corroboration: 65 games, scale=0.7458, offset=0.1271, correlation=0.2197, flat -110: {'picks': 63, 'hit_rate': 0.6349, 'units': 13.36}.", "calibration_version": "measured-edge-margin-v3", "calibration_windows": {"diagnostic": {"correlation": 0.208, "flat_110_diagnostic": {"hit_rate": 0.6, "picks": 285, "units": 41.45}, "games": 290, "offset": 0.1593, "scale": 0.6814}, "real_market": {"correlation": 0.2197, "flat_110_diagnostic": {"hit_rate": 0.6349, "picks": 63, "units": 13.36}, "games": 65, "offset": 0.1271, "scale": 0.7458}}, "model_name": "Measured Edge Margin", "model_version": "measured-edge-margin-v3", "offset": 0.1593, "scale": 0.6814, "trained_on_games": 290}, "artifact_hash": "dd339a2eed50d7d83ab2127837995ddab82e879afd27f5414bb6c1f9cd60ba4c", "away_spread_line": 1.5, "code_sha256": "58bccd1bb97abfc14ea818deb7642e49ab5cbaa6126f4e3d79f33944ad129267", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "features": {"away_bullpen_status": "available", "away_bullpen_weakness": 0.754003, "away_form": {"losses": 1, "runs_allowed": [2, 3, 4, 1, 1, 4], "runs_scored": [3, 4, 3, 3, 2, 7], "status": "available", "wins": 5}, "away_starter": {"last_five_batters_faced": 103, "last_five_earned_runs": 4, "last_five_innings": 26.666666666666668, "last_five_strikeouts": 24, "last_five_walks": 9, "name": "Robert Gasser", "player_id": "4918251", "season_batters_faced": 480, "season_earned_runs": 48, "season_innings": 113.33333333333333, "season_strikeouts": 106, "season_walks": 36, "starts_before_game": 22, "status": "available", "throwing_hand": "Left", "xfip": null, "xfip_status": "unavailable_from_source"}, "away_team": "Milwaukee Brewers", "decision_timestamp_utc": "2026-10-14T22:00:00Z", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "feature_snapshot_hash": "06de8ae80fc43255f9854b4a269c27e6d8d74fe3dfe9e0571a3b9e29b200f020", "home_bullpen_status": "available", "home_bullpen_weakness": 0.543735, "home_form": {"losses": 3, "runs_allowed": [3, 3, 1, 1, 2, 7], "runs_scored": [5, 2, 3, 4, 1, 4], "status": "available", "wins": 3}, "home_starter": {"last_five_batters_faced": 83, "last_five_earned_runs": 3, "last_five_innings": 20.333333333333332, "last_five_strikeouts": 24, "last_five_walks": 9, "name": "Blake Snell", "player_id": "33748", "season_batters_faced": 192, "season_earned_runs": 10, "season_innings": 46.333333333333336, "season_strikeouts": 60, "season_walks": 21, "starts_before_game": 10, "status": "available", "throwing_hand": "Left", "xfip": null, "xfip_status": "unavailable_from_source"}, "home_team": "Los Angeles Dodgers", "lineup_status": "unavailable_from_source", "market_snapshot_hash": "41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0", "park_factor": 1.023, "park_factor_status": "available", "source_snapshot_ids": ["426e4caf3db52fcf13cc3d6110c0c8dfebb17f6e012c71d62e9c5f829d28d875", "5bee6548d750c58ecc0b04fb053bc490a4ba53b6b358c42f57ee6e304a879559", "efcd7d616be57175fbdd44471560ac1ae76d24b89f6a254360415994460b696e", "f1a7e31918b14d7624dbfd79cab472bc83bcbc72378dbf3017f6cb119f29cb6e", "cd3f9d3d1878bc5d0763fa220c7d747cc9c72ac8692a20d370c4a8aaa613db7b"], "starter_confirmed": false, "starter_status": "probable", "weather_factor": 1.007, "weather_status": "available", "wrc_plus_status": "unavailable_from_source"}, "formula_spec": {"away_field_run_factor": 1.0, "bullpen_elasticity": 0.069018, "configuration_hash": "3b7bd3de474b03054313a1806d79c06d8b472b811a4a764926d95f599482d236", "factor_bounds": {"bullpen_weakness": [0.5, 2.0], "offense": [0.7, 1.4], "park": [0.8, 1.3], "starter_weakness": [0.5, 2.0], "weather": [0.85, 1.2]}, "feature_schema_version": "v3", "formula_version": "mlb-analyst-poisson-trend-v0.3", "home_field_run_factor": 1.04, "league_runs_per_team_game": 4.5347, "league_starter_era": 4.2036, "league_strikeout_rate": 0.219, "league_walk_rate": 0.079, "offense_elasticity": 0.088237, "park_elasticity": 0.259048, "recent_half_life_games": 10.0, "recent_prior_strength_games": 12.0, "seed_method": "stable_hash", "simulation": {"extra_inning_home_probability_bounds": [0.5, 0.55], "seed": 42, "shared_environment_variance": 0.06, "simulations": 20000, "team_specific_variance": 0.12}, "starter_rate_prior_batters_faced": 60.0, "starter_recent_prior_innings": 20.0, "starter_recent_weight": 0.7, "starter_season_prior_innings": 40.0, "starter_season_weight": 0.3, "starter_weakness_elasticity": 0.281107, "strikeout_weight": 0.15, "uncertainty": {"base": 0.02, "bullpen_unavailable": 0.02, "lineup_projected": 0.015, "lineup_unavailable": 0.025, "maximum": 0.15, "minimum": 0.02, "missing_wrc_plus": 0.01, "missing_xfip": 0.01, "model_form": 0.01, "pitcher": 0.015, "rookie_starter": 0.03, "weather_unavailable": 0.01}, "walk_weight": 0.1, "weather_elasticity": 0.040295}, "historical_source_observation_times_verified": false, "market_type": "spread", "model_version": "measured-edge-margin-v3", "observed_at_utc": "2026-10-14T05:51:02.821322+00:00", "raw_probabilities": {"away": 0.64245, "home": 0.35755, "push": 0.0}, "replay_scope": "Exact features, formula and deterministic Monte Carlo seed inputs; independently calibrated sides are not a joint distribution.", "run_estimate": {"away_expected_runs": 3.714607, "configuration_hash": "3b7bd3de474b03054313a1806d79c06d8b472b811a4a764926d95f599482d236", "factors": {"away_bullpen_weakness_index": 0.754003, "away_field_run_factor": 1.0, "away_offense_index": 0.9425246552787943, "away_starter_weakness_index": 0.6865741944073087, "home_bullpen_weakness_index": 0.543735, "home_field_run_factor": 1.04, "home_offense_index": 0.8967492210167299, "home_starter_weakness_index": 0.5692565140693949, "park_factor": 1.023, "weather_factor": 1.007}, "feature_schema_version": "v3", "formula_version": "mlb-analyst-poisson-trend-v0.3", "home_expected_runs": 4.146812, "uncertainty": 0.042131, "uncertainty_components": {"base": 0.02, "lineup": 0.025, "missing_wrc_plus": 0.01, "missing_xfip": 0.01, "model_form": 0.01, "pitcher": 0.015, "starter_confirmation": 0.015}}, "schema": "mlb-margin-replay-v1", "served_probabilities": {"away": 0.597065, "home": 0.402935}, "snapshot_hash": "71ea2ab548587ace34fe4c5a4bddf026cee93a2c67ad034e7a0ee486b3304c9e", "sport": "MLB"}</t>
-        </is>
-      </c>
+      <c r="DQ56" s="24" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>30161cd696be4aa1</t>
+          <t>281b8f20babd4f6a</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:02.821322Z</t>
+          <t>2026-10-14T22:45:17.815085Z</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -22380,16 +22418,16 @@
       </c>
       <c r="H57" s="24" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>nrfi</t>
         </is>
       </c>
       <c r="I57" s="24" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>yrfi</t>
         </is>
       </c>
       <c r="J57" s="25" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
@@ -22397,32 +22435,32 @@
         </is>
       </c>
       <c r="L57" s="26" t="n">
-        <v>-106</v>
+        <v>117</v>
       </c>
       <c r="M57" s="27" t="n">
-        <v>1.943396</v>
+        <v>2.17</v>
       </c>
       <c r="N57" s="28" t="n">
-        <v>0.514563</v>
+        <v>0.460829</v>
       </c>
       <c r="O57" s="28" t="n">
-        <v>0.509489</v>
+        <v>0.4812</v>
       </c>
       <c r="P57" s="28" t="n">
-        <v>0.042131</v>
+        <v>0.04</v>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>-0.005074</v>
+        <v>0.020371</v>
       </c>
       <c r="R57" s="26" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S57" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v3</t>
+          <t>mlb-nrfi-v4</t>
         </is>
       </c>
       <c r="U57" s="24" t="inlineStr">
@@ -22441,12 +22479,12 @@
       <c r="AD57" s="24" t="n"/>
       <c r="AE57" s="31" t="inlineStr">
         <is>
-          <t>Measured Edge Totals: Trend Engine projected 3.71-4.15; raw selected-side p=0.5149, calibrated p=0.5095.</t>
+          <t>MLB 1st Inning YRFI: p=0.481 vs ask 0.460 (astatc-mlb-mil-lad-2026-10-14-yrfi; edge +0.0212) (mlb-nrfi-v4, 4272 training games)</t>
         </is>
       </c>
       <c r="AF57" s="31" t="inlineStr">
         <is>
-          <t>Research-only; lineup, bullpen, park, weather, xFIP, and wRC+ may be neutral fallbacks; market availability and BBO depth may change before first pitch.</t>
+          <t>1st inning variance, leadoff home run risk</t>
         </is>
       </c>
       <c r="AG57" s="24" t="inlineStr">
@@ -22459,7 +22497,7 @@
       <c r="AJ57" s="31" t="n"/>
       <c r="AK57" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL57" s="26" t="n">
@@ -22467,7 +22505,7 @@
       </c>
       <c r="AM57" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN57" s="24" t="inlineStr">
@@ -22477,7 +22515,7 @@
       </c>
       <c r="AO57" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP57" s="24" t="inlineStr">
@@ -22520,32 +22558,32 @@
       <c r="AY57" s="24" t="n"/>
       <c r="AZ57" s="24" t="inlineStr">
         <is>
-          <t>research</t>
+          <t>shadow_qualified</t>
         </is>
       </c>
       <c r="BA57" s="24" t="inlineStr">
         <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+          <t>cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff</t>
         </is>
       </c>
       <c r="BB57" s="24" t="inlineStr">
         <is>
-          <t>flat_probability_shrinkage_toward_half</t>
+          <t>half_inning_interaction</t>
         </is>
       </c>
       <c r="BC57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-totals-v3</t>
+          <t>mlb-nrfi-v4</t>
         </is>
       </c>
       <c r="BD57" s="24" t="inlineStr">
         <is>
-          <t>95b84332c75d2ce54036eb8de6ada9c78d0f80228c50825c0347281a8b9b49c7</t>
+          <t>cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff</t>
         </is>
       </c>
       <c r="BE57" s="24" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BF57" s="24" t="inlineStr">
@@ -22555,12 +22593,12 @@
       </c>
       <c r="BG57" s="24" t="inlineStr">
         <is>
-          <t>measured-edge-paired-v1</t>
+          <t>scalar-artifact-replay-v1</t>
         </is>
       </c>
       <c r="BH57" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:51:02.821322Z</t>
+          <t>2026-10-14T22:06:10.080374Z</t>
         </is>
       </c>
       <c r="BI57" s="24" t="inlineStr">
@@ -22569,20 +22607,18 @@
         </is>
       </c>
       <c r="BJ57" s="25" t="n">
-        <v>7.5</v>
+        <v>0.5</v>
       </c>
       <c r="BK57" s="26" t="n">
-        <v>-106</v>
+        <v>117</v>
       </c>
       <c r="BL57" s="27" t="n">
-        <v>1.943396</v>
+        <v>2.17</v>
       </c>
       <c r="BM57" s="28" t="n">
-        <v>0.514563</v>
-      </c>
-      <c r="BN57" s="28" t="n">
-        <v>0.5124379999999999</v>
-      </c>
+        <v>0.460829</v>
+      </c>
+      <c r="BN57" s="28" t="n"/>
       <c r="BO57" s="28" t="n"/>
       <c r="BP57" s="25" t="n"/>
       <c r="BQ57" s="27" t="n"/>
@@ -22615,105 +22651,69 @@
       <c r="CR57" s="24" t="n"/>
       <c r="CS57" s="24" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT57" s="24" t="n"/>
+      <c r="CU57" s="24" t="n"/>
+      <c r="CV57" s="24" t="n"/>
+      <c r="CW57" s="24" t="n"/>
+      <c r="CX57" s="24" t="n"/>
+      <c r="CY57" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:06:10.080374Z</t>
+        </is>
+      </c>
+      <c r="CZ57" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="DA57" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="DB57" s="24" t="inlineStr">
+        <is>
+          <t>decision_time_executable_quote</t>
+        </is>
+      </c>
+      <c r="DC57" s="24" t="inlineStr">
+        <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CT57" s="24" t="inlineStr">
-        <is>
-          <t>a9b23362b31654324ebb68d50a78c7a7cbb34dedfe01df9a0d6220e66c25ca47</t>
-        </is>
-      </c>
-      <c r="CU57" s="24" t="inlineStr">
-        <is>
-          <t>7da9fbc6da4044536749c6fcd9abae7c13da55057708570036207f0597844565</t>
-        </is>
-      </c>
-      <c r="CV57" s="24" t="inlineStr">
-        <is>
-          <t>E:\model-prediction\config\model.yaml</t>
-        </is>
-      </c>
-      <c r="CW57" s="24" t="inlineStr">
-        <is>
-          <t>1dad20b56ac0a94181b31c5f71abe66cc0ee1acd8c8792d0aacf42b7a6fc32e6</t>
-        </is>
-      </c>
-      <c r="CX57" s="24" t="inlineStr">
-        <is>
-          <t>E:\model-prediction\config\models\measured-edge-totals-v3.json</t>
-        </is>
-      </c>
-      <c r="CY57" s="24" t="inlineStr">
-        <is>
-          <t>2026-10-14T05:51:02.821322Z</t>
-        </is>
-      </c>
-      <c r="CZ57" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="DA57" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="DB57" s="24" t="inlineStr">
-        <is>
-          <t>decision_time_executable_quote</t>
-        </is>
-      </c>
-      <c r="DC57" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="DD57" s="24" t="inlineStr">
         <is>
-          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
+          <t>15dbfc80ba914745038ee7c7277b7d56c905b1d1516f03b20f4559f3ae2ae0c6</t>
         </is>
       </c>
       <c r="DE57" s="24" t="inlineStr">
         <is>
-          <t>E:\model-prediction\data\market_odds_snapshots.jsonl</t>
+          <t>E:\model-prediction\data\odds\mlb\2026-10-14\polymarket_snapshots.jsonl</t>
         </is>
       </c>
       <c r="DF57" s="24" t="inlineStr">
         <is>
-          <t>41f27a0b52bff732ed9a9a98d7fd9b0299a3e32788d732c8bd8e37172597aee0</t>
-        </is>
-      </c>
-      <c r="DG57" s="24" t="inlineStr">
-        <is>
-          <t>live_forecast</t>
-        </is>
-      </c>
-      <c r="DH57" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="DI57" s="24" t="inlineStr">
-        <is>
-          <t>0.509489</t>
-        </is>
-      </c>
-      <c r="DJ57" s="24" t="inlineStr">
-        <is>
-          <t>0.5145631067961165</t>
-        </is>
-      </c>
-      <c r="DK57" s="24" t="inlineStr">
-        <is>
-          <t>0.509489</t>
-        </is>
-      </c>
+          <t>15dbfc80ba914745038ee7c7277b7d56c905b1d1516f03b20f4559f3ae2ae0c6</t>
+        </is>
+      </c>
+      <c r="DG57" s="24" t="n"/>
+      <c r="DH57" s="24" t="n"/>
+      <c r="DI57" s="24" t="n"/>
+      <c r="DJ57" s="24" t="n"/>
+      <c r="DK57" s="24" t="n"/>
       <c r="DL57" s="24" t="n"/>
       <c r="DM57" s="24" t="n"/>
       <c r="DN57" s="24" t="n"/>
       <c r="DO57" s="24" t="n"/>
       <c r="DP57" s="24" t="n"/>
-      <c r="DQ57" s="24" t="n"/>
+      <c r="DQ57" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact": {"C": 1.0, "artifact_hash": "cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff", "coef_away": [-0.15092599233710682, 0.33375332491407694, 0.052641650764709516, 0.012200963333336163, -0.044124086984268916, -0.18338539828154118, -0.011069775160598767, -0.07334888990228486, 0.2843164406703071, -0.016022382971498418, -0.42919391686573305, -0.13322539735898248], "coef_home": [-0.056762054222791236, 0.1634913765713207, -0.12677479939259476, -0.10980892029364075, 0.0675840668410901, -0.2155237746431725, -0.0015823333282579347, -0.0017682883771573481, 0.30292713155931383, -0.26515719099464424, -0.24182390473213353, 0.146893598319729], "feature_names": ["top3_composite", "starter_opp_1st_runs", "starter_fip", "starter_k_pct", "starter_bb_pct", "park_1st_runs", "top3_same_hand_share", "team_1st_scored", "top3_park_interaction", "whiff_power_interaction", "starter_park_interaction", "fip_k_ratio"], "fit_n_games": 4272, "intercept_away": 1.0122829388370416, "intercept_home": 0.8796220049130925, "league": "MLB", "market_type": "nrfi", "method": "half_inning_interaction", "model_version": "mlb-nrfi-v4", "note": "Production-qualified MLB first-inning interaction component model replacing mlb-nrfi-v3.", "positive_class": "nrfi", "qualification": {"binary_accuracy": 0.5485, "calibration_ece": 0.021121, "framework": "half_inning_interaction_holdout", "holdout_brier_score": 0.247866, "holdout_log_loss": 0.688855, "locked_holdout": true, "note": "Two-half-inning decomposed model with non-linear interaction features (park, strikeout-whiff, platoon hand alignment) evaluated on 1,424 locked holdout test games.", "qualified": true, "sample_size": 1424, "status": "qualified"}, "scaler_mean_away": [0.10693852528089877, 0.5160531601123584, 3.887999765917613, 0.22160819288389438, 0.07721193820224699, 1.0095550561797733, 0.5512290262172258, 0.4530846910112346, 0.10797593867883881, 0.0832338340753744, 0.522421086896067, 12.74853166149649], "scaler_mean_home": [0.10687735955056178, 0.4668664091760332, 3.880392556179783, 0.22145009363295864, 0.07637907303370803, 1.0095550561797733, 0.5500498361423202, 0.5488433520599267, 0.10794226697635774, 0.08320755243679794, 0.47126779163623655, 12.714614928114717], "scaler_scale_away": [0.0048171779396999235, 0.12136652246642901, 1.0539601780342398, 0.05165113643883803, 0.02673985154876719, 0.09232773263326173, 0.10967171480498189, 0.0982166066212668, 0.01119895692211545, 0.0065842717464252515, 0.13841807595534883, 5.363640846622892], "scaler_scale_home": [0.0049927679114434974, 0.11700796360197874, 1.0206033876941032, 0.052293646761000234, 0.02791997429590162, 0.09232773263326173, 0.11057352848346676, 0.10479111868852325, 0.011525124767030699, 0.006780208072838942, 0.12566593459901798, 5.16406006135981], "schema_version": "2", "sport": "mlb"}, "artifact_hash": "cd40bb944db502574b9d872cd33304728e4cdb96ce0e4e53046dfb089bd166ff", "engine_source_sha256": "0d1788de892d97e815079a85f389a8dcfd16276fa807f5d446a8a943717fd8da", "event_id": "401908032", "event_start_utc": "2026-10-15T00:00Z", "features": {"away_starter_bb_pct": 0.068, "away_starter_days_rest": 6.0, "away_starter_fip": 4.011, "away_starter_k_pct": 0.2039, "away_starter_opp_1st_runs": 0.3185, "away_starter_starts": 3.2958, "away_team_1st_allowed_away": 0.3905, "away_team_1st_scored_away": 0.4186, "away_top3_composite": 0.10642, "home_starter_bb_pct": 0.1018, "home_starter_days_rest": 6.0, "home_starter_fip": 2.288, "home_starter_k_pct": 0.3219, "home_starter_opp_1st_runs": 0.3549, "home_starter_starts": 3.7136, "home_team_1st_allowed_home": 0.5969, "home_team_1st_scored_home": 0.7213, "home_top3_composite": 0.11451, "park_1st_runs": 1.2151}, "historical_source_observation_times_verified": false, "inference_inputs": {}, "model_version": "mlb-nrfi-v4", "observed_at_utc": "2026-10-14T22:45:17.815085+00:00", "replay_scope": "Exact final classifier/distribution inputs and artifact. Upstream historical feature construction not certified.", "schema": "scalar-artifact-replay-v1", "snapshot_hash": "a2b3af2b61189bd6cf37aaf516e66e15fd5959540fb0282643b29263d8a43676"}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
